--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL4" headerRowCount="1">
-  <autoFilter ref="A1:EL4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL7" headerRowCount="1">
+  <autoFilter ref="A1:EL7"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -270,22 +270,22 @@
     <tableColumn id="124" name="over45"/>
     <tableColumn id="125" name="over55"/>
     <tableColumn id="126" name="btts"/>
-    <tableColumn id="127" name="pinnacle_ft_over15"/>
-    <tableColumn id="128" name="pinnacle_ft_over25"/>
-    <tableColumn id="129" name="pinnacle_ft_over35"/>
-    <tableColumn id="130" name="pinnacle_corners_under_95"/>
-    <tableColumn id="131" name="pinnacle_corners_under_85"/>
-    <tableColumn id="132" name="pinnacle_corners_over_95"/>
-    <tableColumn id="133" name="pinnacle_corners_over_85"/>
-    <tableColumn id="134" name="pinnacle_1st_half_over15"/>
-    <tableColumn id="135" name="pinnacle_1st_half_under15"/>
-    <tableColumn id="136" name="pinnacle_1st_half_under05"/>
-    <tableColumn id="137" name="pinnacle_1st_half_over05"/>
-    <tableColumn id="138" name="pinnacle_ft_2"/>
-    <tableColumn id="139" name="pinnacle_ft_1"/>
-    <tableColumn id="140" name="pinnacle_ft_x"/>
-    <tableColumn id="141" name="pinnacle_btts_no"/>
-    <tableColumn id="142" name="pinnacle_btts_yes"/>
+    <tableColumn id="127" name="pinnacle_btts_yes"/>
+    <tableColumn id="128" name="pinnacle_btts_no"/>
+    <tableColumn id="129" name="pinnacle_ft_2"/>
+    <tableColumn id="130" name="pinnacle_ft_x"/>
+    <tableColumn id="131" name="pinnacle_ft_1"/>
+    <tableColumn id="132" name="pinnacle_ft_over35"/>
+    <tableColumn id="133" name="pinnacle_ft_over15"/>
+    <tableColumn id="134" name="pinnacle_ft_over25"/>
+    <tableColumn id="135" name="pinnacle_corners_over_85"/>
+    <tableColumn id="136" name="pinnacle_corners_under_85"/>
+    <tableColumn id="137" name="pinnacle_corners_over_95"/>
+    <tableColumn id="138" name="pinnacle_corners_under_95"/>
+    <tableColumn id="139" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="140" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="141" name="pinnacle_1st_half_over05"/>
+    <tableColumn id="142" name="pinnacle_1st_half_under05"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -580,13 +580,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL4"/>
+  <dimension ref="A1:EL7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
     <col width="9.6" customWidth="1" min="2" max="2"/>
     <col width="13.2" customWidth="1" min="3" max="3"/>
-    <col width="19.2" customWidth="1" min="4" max="4"/>
+    <col width="20.4" customWidth="1" min="4" max="4"/>
     <col width="20.4" customWidth="1" min="5" max="5"/>
     <col width="25.2" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -610,7 +610,7 @@
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
     <col width="36" customWidth="1" min="27" max="27"/>
-    <col width="40.8" customWidth="1" min="28" max="28"/>
+    <col width="46.8" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -708,23 +708,23 @@
     <col width="9.6" customWidth="1" min="123" max="123"/>
     <col width="9.6" customWidth="1" min="124" max="124"/>
     <col width="9.6" customWidth="1" min="125" max="125"/>
-    <col width="7.199999999999999" customWidth="1" min="126" max="126"/>
-    <col width="24" customWidth="1" min="127" max="127"/>
-    <col width="24" customWidth="1" min="128" max="128"/>
-    <col width="24" customWidth="1" min="129" max="129"/>
-    <col width="32.4" customWidth="1" min="130" max="130"/>
-    <col width="32.4" customWidth="1" min="131" max="131"/>
-    <col width="31.2" customWidth="1" min="132" max="132"/>
-    <col width="31.2" customWidth="1" min="133" max="133"/>
-    <col width="31.2" customWidth="1" min="134" max="134"/>
-    <col width="32.4" customWidth="1" min="135" max="135"/>
+    <col width="8.4" customWidth="1" min="126" max="126"/>
+    <col width="22.8" customWidth="1" min="127" max="127"/>
+    <col width="21.6" customWidth="1" min="128" max="128"/>
+    <col width="18" customWidth="1" min="129" max="129"/>
+    <col width="18" customWidth="1" min="130" max="130"/>
+    <col width="18" customWidth="1" min="131" max="131"/>
+    <col width="24" customWidth="1" min="132" max="132"/>
+    <col width="24" customWidth="1" min="133" max="133"/>
+    <col width="24" customWidth="1" min="134" max="134"/>
+    <col width="31.2" customWidth="1" min="135" max="135"/>
     <col width="32.4" customWidth="1" min="136" max="136"/>
     <col width="31.2" customWidth="1" min="137" max="137"/>
-    <col width="18" customWidth="1" min="138" max="138"/>
-    <col width="18" customWidth="1" min="139" max="139"/>
-    <col width="18" customWidth="1" min="140" max="140"/>
-    <col width="21.6" customWidth="1" min="141" max="141"/>
-    <col width="22.8" customWidth="1" min="142" max="142"/>
+    <col width="32.4" customWidth="1" min="138" max="138"/>
+    <col width="32.4" customWidth="1" min="139" max="139"/>
+    <col width="31.2" customWidth="1" min="140" max="140"/>
+    <col width="31.2" customWidth="1" min="141" max="141"/>
+    <col width="32.4" customWidth="1" min="142" max="142"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1360,82 +1360,82 @@
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_btts_yes</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_btts_no</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_2</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_x</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_1</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_ft_over35</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_ft_over15</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_ft_over25</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_over35</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_over_85</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_under_85</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_corners_over_95</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_95</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_under_85</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_over_95</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_corners_over_85</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under15</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_1st_half_over15</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under15</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over05</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_1st_half_under05</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over05</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_2</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_1</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_ft_x</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_btts_no</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_btts_yes</t>
         </is>
       </c>
     </row>
@@ -1500,19 +1500,19 @@
         <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W2" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
         <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -1684,13 +1684,13 @@
         <v>152</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1735,31 +1735,31 @@
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR2" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CS2" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="CT2" t="n">
         <v>1</v>
       </c>
       <c r="CU2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CV2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CW2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CZ2" t="n">
         <v>0</v>
@@ -1832,82 +1832,82 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>4.04</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>2.67</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>1.86</t>
         </is>
       </c>
     </row>
@@ -1972,19 +1972,19 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
         <v>8</v>
       </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>7</v>
-      </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
         <v>14</v>
@@ -1993,10 +1993,10 @@
         <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -2156,13 +2156,13 @@
         <v>84</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="CB3" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="CC3" t="n">
         <v>1</v>
@@ -2207,31 +2207,31 @@
         <v>1</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR3" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="CS3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CT3" t="n">
         <v>1</v>
       </c>
       <c r="CU3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CV3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ3" t="n">
         <v>0</v>
@@ -2304,68 +2304,68 @@
       </c>
       <c r="DW3" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
         <is>
           <t>2.29</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>4.16</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
         <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr"/>
-      <c r="EE3" t="inlineStr"/>
-      <c r="EF3" t="inlineStr"/>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2425,22 +2425,22 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W4" t="n">
         <v>9</v>
@@ -2449,10 +2449,10 @@
         <v>9</v>
       </c>
       <c r="Y4" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="Z4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
@@ -2604,13 +2604,13 @@
         <v>102</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2655,179 +2655,1571 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46082.20833333334</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="n">
+        <v>11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Jeonju World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3852</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
         <v>-1</v>
       </c>
-      <c r="CR4" t="n">
+      <c r="BG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>124</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU5" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>7.54</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>46082.3125</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>-1</v>
       </c>
-      <c r="CS4" t="n">
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
         <v>-1</v>
       </c>
-      <c r="CT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU4" t="n">
+      <c r="BG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>46083.20833333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
         <v>9</v>
       </c>
-      <c r="CV4" t="n">
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>13</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
         <v>12</v>
       </c>
-      <c r="CW4" t="n">
+      <c r="X7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Daejeon World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
         <v>-1</v>
       </c>
-      <c r="CX4" t="n">
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
         <v>-1</v>
       </c>
-      <c r="CY4" t="n">
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>144</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
         <v>-1</v>
       </c>
-      <c r="CZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP4" t="b">
-        <v>1</v>
-      </c>
-      <c r="DQ4" t="b">
-        <v>1</v>
-      </c>
-      <c r="DR4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU4" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW4" t="inlineStr">
+      <c r="CR7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="DY4" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
-          <t>1.89</t>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>2.98</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -3825,22 +3825,22 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>16</v>
+      </c>
+      <c r="V7" t="n">
         <v>8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>13</v>
-      </c>
-      <c r="V7" t="n">
-        <v>9</v>
       </c>
       <c r="W7" t="n">
         <v>12</v>
@@ -3849,10 +3849,10 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -4012,13 +4012,13 @@
         <v>106</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.11</v>
+        <v>3.37</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4063,31 +4063,31 @@
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CS7" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CT7" t="n">
         <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CV7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY7" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL7" headerRowCount="1">
-  <autoFilter ref="A1:EL7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL9" headerRowCount="1">
+  <autoFilter ref="A1:EL9"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL7"/>
+  <dimension ref="A1:EL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -4223,6 +4223,926 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>46088.3125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Bucheon Stadium</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>146</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46088.3125</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Gwangju World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>, Gwangju</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3841</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>93</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>124</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU9" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL9" headerRowCount="1">
-  <autoFilter ref="A1:EL9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL11" headerRowCount="1">
+  <autoFilter ref="A1:EL11"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL9"/>
+  <dimension ref="A1:EL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="b">
         <v>0</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4281,22 +4281,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -4305,10 +4305,10 @@
         <v>7</v>
       </c>
       <c r="Y8" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -4468,13 +4468,13 @@
         <v>146</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="CB8" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="CC8" t="n">
         <v>1</v>
@@ -4519,31 +4519,31 @@
         <v>-1</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR8" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CS8" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CT8" t="n">
         <v>1</v>
       </c>
       <c r="CU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV8" t="n">
         <v>8</v>
       </c>
-      <c r="CV8" t="n">
-        <v>9</v>
-      </c>
       <c r="CW8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX8" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY8" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ8" t="n">
         <v>0</v>
@@ -4725,7 +4725,7 @@
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>4</v>
@@ -4740,19 +4740,19 @@
         <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U9" t="n">
         <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="W9" t="n">
         <v>14</v>
@@ -4761,10 +4761,10 @@
         <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Z9" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
         <v>4</v>
@@ -4897,7 +4897,7 @@
         <v>2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR9" t="n">
         <v>2</v>
@@ -4906,7 +4906,7 @@
         <v>2</v>
       </c>
       <c r="BT9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU9" t="n">
         <v>1</v>
@@ -4927,10 +4927,10 @@
         <v>1.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="CB9" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="CC9" t="n">
         <v>1</v>
@@ -4975,31 +4975,31 @@
         <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR9" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CS9" t="n">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
       </c>
       <c r="CU9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CW9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5140,6 +5140,942 @@
       <c r="EL9" t="inlineStr">
         <is>
           <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46089.20833333334</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>46089.3125</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Anyang Stadium</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3848</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
+        <is>
+          <t>2.67</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -5201,22 +5201,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
         <v>5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6</v>
       </c>
       <c r="W10" t="n">
         <v>8</v>
@@ -5380,13 +5380,13 @@
         <v>114</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="CB10" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5431,31 +5431,31 @@
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR10" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CS10" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
       </c>
       <c r="CU10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5665,22 +5665,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>12</v>
+      </c>
+      <c r="V11" t="n">
         <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
       </c>
       <c r="W11" t="n">
         <v>11</v>
@@ -5852,13 +5852,13 @@
         <v>106</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="CB11" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="CC11" t="n">
         <v>1</v>
@@ -5903,31 +5903,31 @@
         <v>0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR11" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CS11" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CT11" t="n">
         <v>1</v>
       </c>
       <c r="CU11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CV11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CW11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CY11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CZ11" t="n">
         <v>0</v>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL11" headerRowCount="1">
-  <autoFilter ref="A1:EL11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL13" headerRowCount="1">
+  <autoFilter ref="A1:EL13"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL11"/>
+  <dimension ref="A1:EL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -5014,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>1.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6076,6 +6076,926 @@
       <c r="EL11" t="inlineStr">
         <is>
           <t>2.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>46095.20833333334</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Gwangju World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>, Gwangju</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>78</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>22</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr"/>
+      <c r="EH12" t="inlineStr"/>
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ12" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EL12" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>46095.3125</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>12</v>
+      </c>
+      <c r="V13" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" t="n">
+        <v>9</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Daejeon World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>148</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr"/>
+      <c r="EF13" t="inlineStr"/>
+      <c r="EG13" t="inlineStr"/>
+      <c r="EH13" t="inlineStr"/>
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ13" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EK13" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
+        <is>
+          <t>3.19</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL13" headerRowCount="1">
-  <autoFilter ref="A1:EL13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL17" headerRowCount="1">
+  <autoFilter ref="A1:EL17"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL13"/>
+  <dimension ref="A1:EL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP6" t="b">
         <v>0</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DE8" t="n">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5017,7 +5017,7 @@
         <v>2</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5975,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6137,22 +6137,22 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
         <v>20</v>
@@ -6161,10 +6161,10 @@
         <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>51</v>
       </c>
       <c r="BW12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="BX12" t="n">
         <v>110</v>
@@ -6324,13 +6324,13 @@
         <v>101</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CB12" t="n">
-        <v>1.66</v>
+        <v>2.77</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6375,31 +6375,31 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR12" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CS12" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CT12" t="n">
         <v>1</v>
       </c>
       <c r="CU12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CW12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX12" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CY12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ12" t="n">
         <v>50</v>
@@ -6472,17 +6472,17 @@
       </c>
       <c r="DW12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DX12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="DY12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="DZ12" t="inlineStr">
@@ -6492,22 +6492,22 @@
       </c>
       <c r="EA12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EB12" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="EC12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED12" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EE12" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="EK12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EL12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -6601,19 +6601,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
         <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V13" t="n">
         <v>10</v>
@@ -6625,10 +6625,10 @@
         <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -6788,13 +6788,13 @@
         <v>93</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CA13" t="n">
         <v>1.17</v>
       </c>
       <c r="CB13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -6839,31 +6839,31 @@
         <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR13" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CS13" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="CT13" t="n">
         <v>1</v>
       </c>
       <c r="CU13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CV13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY13" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ13" t="n">
         <v>0</v>
@@ -6936,66 +6936,1882 @@
       </c>
       <c r="DW13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="DX13" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="DY13" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="DZ13" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EA13" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EB13" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EC13" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="ED13" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EE13" t="inlineStr"/>
       <c r="EF13" t="inlineStr"/>
       <c r="EG13" t="inlineStr"/>
       <c r="EH13" t="inlineStr"/>
-      <c r="EI13" t="inlineStr">
+      <c r="EI13" t="inlineStr"/>
+      <c r="EJ13" t="inlineStr"/>
+      <c r="EK13" t="inlineStr"/>
+      <c r="EL13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>46096.20833333334</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" t="n">
+        <v>15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3833</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>7518</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>66</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW14" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr"/>
+      <c r="EK14" t="inlineStr"/>
+      <c r="EL14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>46096.20833333334</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10</v>
+      </c>
+      <c r="V15" t="n">
+        <v>13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>15</v>
+      </c>
+      <c r="X15" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Bucheon Stadium</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3836</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>73</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>147</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP15" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ15" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR15" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW15" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DY15" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EA15" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EB15" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EJ15" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EK15" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="EJ13" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EK13" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EL13" t="inlineStr">
-        <is>
-          <t>3.19</t>
+      <c r="EL15" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>46096.3125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP16" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ16" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW16" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DX16" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DY16" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ16" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EK16" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>46096.3125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP17" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ17" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW17" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="DX17" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DY17" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EA17" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EB17" t="inlineStr">
+        <is>
+          <t>4.74</t>
+        </is>
+      </c>
+      <c r="EC17" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr"/>
+      <c r="EF17" t="inlineStr"/>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr"/>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t>2.46</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL17" headerRowCount="1">
-  <autoFilter ref="A1:EL17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL23" headerRowCount="1">
+  <autoFilter ref="A1:EL23"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL17"/>
+  <dimension ref="A1:EL23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>3</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DE5" t="n">
         <v>3</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DE6" t="n">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP6" t="b">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4558,10 +4558,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5503,7 +5503,7 @@
         <v>1.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5975,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>1.94</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP12" t="b">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>1.93</v>
       </c>
       <c r="DO13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -7020,19 +7020,19 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7044,111 +7044,119 @@
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V14" t="n">
+        <v>18</v>
+      </c>
+      <c r="W14" t="n">
         <v>15</v>
-      </c>
-      <c r="W14" t="n">
-        <v>19</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z14" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Bucheon Stadium</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+        </is>
+      </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="AF14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3.1</v>
       </c>
-      <c r="AG14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AS14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3833</v>
+        <v>3836</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
@@ -7160,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>7518</v>
+        <v>-1</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -7169,76 +7177,76 @@
         <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
         <v>6</v>
       </c>
-      <c r="BM14" t="n">
-        <v>3</v>
-      </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU14" t="n">
         <v>1</v>
       </c>
       <c r="BV14" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="BW14" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="BX14" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="BY14" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.99</v>
+        <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.76</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG14" t="n">
         <v>0</v>
@@ -7253,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="CK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -7262,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
@@ -7271,13 +7279,13 @@
         <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR14" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CS14" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CT14" t="n">
         <v>1</v>
@@ -7286,19 +7294,19 @@
         <v>13</v>
       </c>
       <c r="CV14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="CW14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX14" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY14" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CZ14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA14" t="n">
         <v>50</v>
@@ -7310,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE14" t="n">
         <v>3</v>
@@ -7319,10 +7327,10 @@
         <v>1</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI14" t="n">
         <v>3</v>
@@ -7331,19 +7339,19 @@
         <v>50</v>
       </c>
       <c r="DK14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="DM14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>2.58</v>
+        <v>1.08</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7368,7 +7376,7 @@
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
@@ -7378,58 +7386,74 @@
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="DZ14" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EA14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB14" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EC14" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr"/>
-      <c r="EJ14" t="inlineStr"/>
-      <c r="EK14" t="inlineStr"/>
-      <c r="EL14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7447,12 +7471,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -7468,19 +7492,19 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>9</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -7498,113 +7522,105 @@
         <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U15" t="n">
         <v>10</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="AF15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>3.3</v>
       </c>
-      <c r="AG15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
         <v>3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>3836</v>
+        <v>3833</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
@@ -7616,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>7518</v>
       </c>
       <c r="BG15" t="n">
         <v>2</v>
@@ -7625,61 +7641,61 @@
         <v>1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BM15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BN15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU15" t="n">
         <v>1</v>
       </c>
       <c r="BV15" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="BW15" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="BX15" t="n">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="CB15" t="n">
         <v>3</v>
@@ -7688,13 +7704,13 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
         <v>0</v>
       </c>
       <c r="CF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
         <v>0</v>
@@ -7709,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="CK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -7718,7 +7734,7 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
@@ -7727,13 +7743,13 @@
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR15" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CS15" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CT15" t="n">
         <v>1</v>
@@ -7742,19 +7758,19 @@
         <v>13</v>
       </c>
       <c r="CV15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CW15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX15" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY15" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA15" t="n">
         <v>50</v>
@@ -7766,19 +7782,19 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH15" t="n">
         <v>0.5</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>2</v>
       </c>
       <c r="DI15" t="n">
         <v>3</v>
@@ -7787,19 +7803,19 @@
         <v>50</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.08</v>
+        <v>2.58</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7824,7 +7840,7 @@
       </c>
       <c r="DW15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="DX15" t="inlineStr">
@@ -7834,74 +7850,58 @@
       </c>
       <c r="DY15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="DZ15" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EA15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EB15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EC15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="ED15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EE15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EF15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EG15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EH15" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI15" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EJ15" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="EK15" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EL15" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr"/>
+      <c r="EL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -7940,140 +7940,132 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.36</v>
+        <v>2.38</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
         <v>-1</v>
@@ -8097,64 +8089,64 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BO16" t="n">
         <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
         <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="BW16" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="BX16" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="BY16" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
       <c r="CB16" t="n">
-        <v>1.96</v>
+        <v>2.57</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8181,16 +8173,16 @@
         <v>1</v>
       </c>
       <c r="CK16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8199,65 +8191,65 @@
         <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CS16" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CV16" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CW16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY16" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CZ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA16" t="n">
         <v>50</v>
       </c>
       <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ16" t="n">
         <v>50</v>
       </c>
-      <c r="DC16" t="n">
-        <v>50</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>0</v>
-      </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
@@ -8265,13 +8257,13 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="DO16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8296,74 +8288,66 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr"/>
+      <c r="EF16" t="inlineStr"/>
       <c r="EG16" t="inlineStr"/>
       <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.46</t>
         </is>
       </c>
     </row>
@@ -8383,12 +8367,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8404,132 +8388,140 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="W17" t="n">
+        <v>12</v>
+      </c>
+      <c r="X17" t="n">
         <v>9</v>
       </c>
-      <c r="X17" t="n">
-        <v>7</v>
-      </c>
       <c r="Y17" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="Z17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
         <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AU17" t="n">
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB17" t="n">
         <v>-1</v>
@@ -8553,64 +8545,64 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BN17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BO17" t="n">
         <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR17" t="n">
         <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BW17" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="BX17" t="n">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="BY17" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.68</v>
+        <v>1.39</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8637,16 +8629,16 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8655,13 +8647,13 @@
         <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CS17" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
@@ -8670,49 +8662,49 @@
         <v>9</v>
       </c>
       <c r="CV17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CW17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY17" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA17" t="n">
         <v>50</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
       </c>
       <c r="DG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
@@ -8721,13 +8713,13 @@
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8752,66 +8744,2866 @@
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EE17" t="inlineStr"/>
-      <c r="EF17" t="inlineStr"/>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46098.4375</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>62</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW18" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="DY18" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="DZ18" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>46099.4375</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>9</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Jeonju World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3837</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>149</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>75</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU19" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI19" t="inlineStr"/>
+      <c r="EJ19" t="inlineStr"/>
+      <c r="EK19" t="inlineStr"/>
+      <c r="EL19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46099.4375</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>3833</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC20" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP20" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV20" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF20" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI20" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="EJ17" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EK17" t="inlineStr">
+      <c r="EJ20" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>46099.4375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7</v>
+      </c>
+      <c r="X21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Sungui Arena Park</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Dowon-dong, Jung-gu, Incheon</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3845</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>136</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU21" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV21" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW21" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EA21" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EB21" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EC21" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="ED21" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF21" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr"/>
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EK21" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46099.4375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>13</v>
+      </c>
+      <c r="X22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Bucheon Stadium</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA22" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>75</v>
+      </c>
+      <c r="DC22" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DM22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV22" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW22" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DZ22" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EA22" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EF22" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
         <is>
           <t>1.57</t>
         </is>
       </c>
-      <c r="EL17" t="inlineStr">
-        <is>
-          <t>2.46</t>
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ22" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EL22" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46099.4375</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>14</v>
+      </c>
+      <c r="V23" t="n">
+        <v>12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3836</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW23" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EJ23" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr">
+        <is>
+          <t>2.99</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -8876,19 +8876,19 @@
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="W18" t="n">
         <v>14</v>
@@ -8897,10 +8897,10 @@
         <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Z18" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
@@ -9052,13 +9052,13 @@
         <v>106</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.58</v>
+        <v>1.86</v>
       </c>
       <c r="CB18" t="n">
-        <v>2.02</v>
+        <v>3.67</v>
       </c>
       <c r="CC18" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR18" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="CS18" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CT18" t="n">
         <v>1</v>
       </c>
       <c r="CU18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CV18" t="n">
         <v>15</v>
       </c>
       <c r="CW18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX18" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY18" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ18" t="n">
         <v>0</v>
@@ -9337,22 +9337,22 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W19" t="n">
         <v>9</v>
@@ -9361,10 +9361,10 @@
         <v>10</v>
       </c>
       <c r="Y19" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Z19" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -9524,13 +9524,13 @@
         <v>99</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.3</v>
+        <v>3.12</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9575,31 +9575,31 @@
         <v>0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="CS19" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY19" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ19" t="n">
         <v>50</v>
@@ -9772,40 +9772,40 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>4</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
       <c r="R20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V20" t="n">
         <v>8</v>
@@ -9817,10 +9817,10 @@
         <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Z20" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -9953,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR20" t="n">
         <v>0</v>
@@ -9962,7 +9962,7 @@
         <v>2</v>
       </c>
       <c r="BT20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
@@ -9980,13 +9980,13 @@
         <v>111</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.27</v>
+        <v>2.6</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -10031,31 +10031,31 @@
         <v>0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CS20" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CV20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CW20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY20" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ20" t="n">
         <v>50</v>
@@ -10265,22 +10265,22 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S21" t="n">
         <v>4</v>
       </c>
-      <c r="R21" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
       <c r="T21" t="n">
         <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
         <v>7</v>
@@ -10452,13 +10452,13 @@
         <v>136</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="CA21" t="n">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
       <c r="CB21" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="CC21" t="n">
         <v>0</v>
@@ -10503,31 +10503,31 @@
         <v>0</v>
       </c>
       <c r="CQ21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR21" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CS21" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CT21" t="n">
         <v>1</v>
       </c>
       <c r="CU21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CV21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX21" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY21" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CZ21" t="n">
         <v>50</v>
@@ -10729,22 +10729,22 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
-        <v>2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22" t="n">
         <v>13</v>
@@ -10753,10 +10753,10 @@
         <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z22" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -10916,13 +10916,13 @@
         <v>98</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.87</v>
+        <v>1.19</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="CB22" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -10967,31 +10967,31 @@
         <v>0</v>
       </c>
       <c r="CQ22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CS22" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CV22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX22" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CZ22" t="n">
         <v>75</v>
@@ -11183,40 +11183,40 @@
         <v>4</v>
       </c>
       <c r="K23" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" t="n">
-        <v>11</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6</v>
-      </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="n">
         <v>7</v>
       </c>
       <c r="U23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
         <v>11</v>
@@ -11225,10 +11225,10 @@
         <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="Z23" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
@@ -11380,13 +11380,13 @@
         <v>83</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11431,31 +11431,31 @@
         <v>0</v>
       </c>
       <c r="CQ23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CS23" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV23" t="n">
         <v>12</v>
       </c>
       <c r="CW23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX23" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY23" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ23" t="n">
         <v>75</v>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL23" headerRowCount="1">
-  <autoFilter ref="A1:EL23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL29" headerRowCount="1">
+  <autoFilter ref="A1:EL29"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL23"/>
+  <dimension ref="A1:EL29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
     <col width="36" customWidth="1" min="27" max="27"/>
-    <col width="46.8" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -1455,212 +1455,212 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
         <v>46081.20833333334</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
+        <v>13</v>
+      </c>
+      <c r="W2" t="n">
         <v>14</v>
       </c>
-      <c r="W2" t="n">
-        <v>10</v>
-      </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Z2" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Ulsan Munsu Football Stadium</t>
+          <t>Sungui Arena Park</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
+          <t>Dowon-dong, Jung-gu, Incheon</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>2.19</v>
       </c>
       <c r="AH2" t="n">
         <v>1.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AU2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3833</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>18108</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK2" t="n">
         <v>4</v>
       </c>
-      <c r="AV2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3836</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1</v>
-      </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS2" t="n">
         <v>2</v>
@@ -1672,34 +1672,34 @@
         <v>1</v>
       </c>
       <c r="BV2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="BW2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX2" t="n">
         <v>99</v>
       </c>
-      <c r="BX2" t="n">
-        <v>81</v>
-      </c>
       <c r="BY2" t="n">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.29</v>
+        <v>2.62</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
@@ -1732,35 +1732,35 @@
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ2" t="n">
         <v>1</v>
       </c>
       <c r="CR2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CS2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CT2" t="n">
         <v>1</v>
       </c>
       <c r="CU2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW2" t="n">
         <v>1</v>
       </c>
       <c r="CX2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY2" t="n">
         <v>9</v>
       </c>
-      <c r="CY2" t="n">
-        <v>2</v>
-      </c>
       <c r="CZ2" t="n">
         <v>0</v>
       </c>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="DS2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="b">
         <v>0</v>
@@ -1832,84 +1832,68 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1927,146 +1911,146 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
         <v>46081.20833333334</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
         <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="Z3" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Sungui Arena Park</t>
+          <t>Ulsan Munsu Football Stadium</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
+          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.19</v>
+        <v>3</v>
       </c>
       <c r="AH3" t="n">
         <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -2075,16 +2059,16 @@
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>3833</v>
+        <v>3836</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -2096,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>18108</v>
+        <v>-1</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
@@ -2105,182 +2089,182 @@
         <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>99</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>152</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO3" t="n">
         <v>4</v>
       </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>51</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>99</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>84</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>3</v>
-      </c>
       <c r="DP3" t="b">
         <v>1</v>
       </c>
@@ -2291,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="DS3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT3" t="b">
         <v>0</v>
@@ -2304,68 +2288,84 @@
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3169,7 +3169,7 @@
         <v>1.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3633,7 +3633,7 @@
         <v>0.33</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP6" t="b">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DE7" t="n">
         <v>0.67</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5017,7 +5017,7 @@
         <v>2</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5473,7 +5473,7 @@
         <v>1</v>
       </c>
       <c r="DE10" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -5503,7 +5503,7 @@
         <v>1.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5975,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6417,7 +6417,7 @@
         <v>2</v>
       </c>
       <c r="DE12" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6447,7 +6447,7 @@
         <v>1.94</v>
       </c>
       <c r="DO12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP12" t="b">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -6911,7 +6911,7 @@
         <v>1.93</v>
       </c>
       <c r="DO13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7351,7 +7351,7 @@
         <v>1.08</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7815,7 +7815,7 @@
         <v>2.58</v>
       </c>
       <c r="DO15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -7940,132 +7940,140 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
+        <v>12</v>
+      </c>
+      <c r="X16" t="n">
         <v>9</v>
       </c>
-      <c r="X16" t="n">
-        <v>7</v>
-      </c>
       <c r="Y16" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="Z16" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="n">
         <v>-1</v>
@@ -8089,64 +8097,64 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK16" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BN16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BO16" t="n">
         <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR16" t="n">
         <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BW16" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="BX16" t="n">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="BY16" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.87</v>
+        <v>1.39</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8173,16 +8181,16 @@
         <v>1</v>
       </c>
       <c r="CK16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8194,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CS16" t="n">
         <v>14</v>
@@ -8203,52 +8211,52 @@
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA16" t="n">
         <v>50</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -8257,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="DO16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8288,66 +8296,74 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr"/>
-      <c r="EF16" t="inlineStr"/>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
       <c r="EG16" t="inlineStr"/>
       <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8383,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8388,140 +8404,132 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
+        <v>14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.92</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.36</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AU17" t="n">
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
         <v>-1</v>
@@ -8545,64 +8553,64 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BO17" t="n">
         <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
         <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="BW17" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="BX17" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="BY17" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.39</v>
+        <v>0.87</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8629,16 +8637,16 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8650,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CS17" t="n">
         <v>14</v>
@@ -8659,53 +8667,53 @@
         <v>1</v>
       </c>
       <c r="CU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV17" t="n">
         <v>9</v>
       </c>
-      <c r="CV17" t="n">
-        <v>13</v>
-      </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="CZ17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA17" t="n">
         <v>50</v>
       </c>
       <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ17" t="n">
         <v>50</v>
       </c>
-      <c r="DC17" t="n">
-        <v>50</v>
-      </c>
-      <c r="DD17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>0</v>
-      </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
@@ -8713,13 +8721,13 @@
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="DO17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8744,74 +8752,66 @@
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EE17" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr"/>
+      <c r="EF17" t="inlineStr"/>
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.46</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9145,7 @@
         <v>1</v>
       </c>
       <c r="DE18" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9175,7 +9175,7 @@
         <v>2.41</v>
       </c>
       <c r="DO18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9295,40 +9295,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>46099.4375</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -9337,122 +9337,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
         <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>11</v>
       </c>
       <c r="T19" t="n">
         <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="Z19" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Jeonju World Cup Stadium</t>
+          <t>Bucheon Stadium</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.74</v>
+        <v>3.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.65</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>3837</v>
+        <v>-1</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9473,136 +9473,136 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ19" t="n">
         <v>2</v>
       </c>
       <c r="BK19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL19" t="n">
         <v>1</v>
       </c>
       <c r="BM19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO19" t="n">
         <v>1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
         <v>2</v>
       </c>
       <c r="BS19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ19" t="n">
         <v>75</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX19" t="n">
-        <v>149</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>99</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>50</v>
       </c>
       <c r="DA19" t="n">
         <v>100</v>
@@ -9614,49 +9614,49 @@
         <v>75</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="DI19" t="n">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="DJ19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK19" t="n">
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="DN19" t="n">
-        <v>2.71</v>
+        <v>3.11</v>
       </c>
       <c r="DO19" t="n">
         <v>4</v>
       </c>
       <c r="DP19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS19" t="b">
         <v>0</v>
@@ -9668,72 +9668,88 @@
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW19" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DX19" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="DY19" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="DZ19" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="EA19" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EB19" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="EC19" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="ED19" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EE19" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EG19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EH19" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EI19" t="inlineStr"/>
-      <c r="EJ19" t="inlineStr"/>
-      <c r="EK19" t="inlineStr"/>
-      <c r="EL19" t="inlineStr"/>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ19" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EK19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EL19" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9751,12 +9767,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -9766,155 +9782,147 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Z20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.28</v>
+        <v>2.04</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AP20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT20" t="n">
         <v>1.42</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>3833</v>
+        <v>3836</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
@@ -9947,46 +9955,46 @@
         <v>-1</v>
       </c>
       <c r="BO20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
         <v>0</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="BW20" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="BX20" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="BY20" t="n">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -10016,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM20" t="n">
         <v>-1</v>
@@ -10034,19 +10042,19 @@
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CS20" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CV20" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
@@ -10055,61 +10063,61 @@
         <v>7</v>
       </c>
       <c r="CY20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ20" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB20" t="n">
         <v>50</v>
-      </c>
-      <c r="DA20" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>0</v>
       </c>
       <c r="DC20" t="n">
         <v>50</v>
       </c>
       <c r="DD20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DE20" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF20" t="n">
         <v>0.5</v>
       </c>
-      <c r="DE20" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF20" t="n">
-        <v>1</v>
-      </c>
       <c r="DG20" t="n">
         <v>3</v>
       </c>
       <c r="DH20" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="DI20" t="n">
         <v>3</v>
       </c>
       <c r="DJ20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="DN20" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="DO20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
       </c>
       <c r="DQ20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR20" t="b">
         <v>0</v>
@@ -10128,82 +10136,82 @@
       </c>
       <c r="DW20" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="DX20" t="inlineStr">
         <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="DY20" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="DZ20" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="EA20" t="inlineStr">
-        <is>
-          <t>3.99</t>
-        </is>
-      </c>
-      <c r="EB20" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="EC20" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="ED20" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EE20" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EG20" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EH20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EI20" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EJ20" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EK20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL20" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.99</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10583,7 @@
         <v>2.56</v>
       </c>
       <c r="DO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10687,12 +10695,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -10702,134 +10710,134 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
+        <v>10</v>
+      </c>
+      <c r="M22" t="n">
         <v>5</v>
       </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
+        <v>13</v>
+      </c>
+      <c r="V22" t="n">
         <v>8</v>
       </c>
-      <c r="U22" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" t="n">
-        <v>10</v>
-      </c>
       <c r="W22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Z22" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Bucheon Stadium</t>
+          <t>Steelyard Stadium</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+          <t>, Pohang</t>
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.82</v>
+        <v>3.28</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
@@ -10841,10 +10849,10 @@
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB22" t="n">
-        <v>-1</v>
+        <v>3833</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
@@ -10859,70 +10867,70 @@
         <v>-1</v>
       </c>
       <c r="BG22" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH22" t="n">
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BK22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL22" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BM22" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BN22" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BO22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BR22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS22" t="n">
         <v>2</v>
       </c>
       <c r="BT22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
       </c>
       <c r="BV22" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="BW22" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="BX22" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="BY22" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="CB22" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -10952,13 +10960,13 @@
         <v>0</v>
       </c>
       <c r="CL22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -10970,61 +10978,61 @@
         <v>1</v>
       </c>
       <c r="CR22" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CS22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CT22" t="n">
         <v>1</v>
       </c>
       <c r="CU22" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV22" t="n">
         <v>17</v>
       </c>
-      <c r="CV22" t="n">
-        <v>14</v>
-      </c>
       <c r="CW22" t="n">
         <v>1</v>
       </c>
       <c r="CX22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CY22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CZ22" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DA22" t="n">
         <v>100</v>
       </c>
       <c r="DB22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DC22" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DD22" t="n">
         <v>0.67</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DF22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DG22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH22" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DJ22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DK22" t="n">
         <v>0</v>
@@ -11033,16 +11041,16 @@
         <v>1.22</v>
       </c>
       <c r="DM22" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="DN22" t="n">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="DO22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ22" t="b">
         <v>0</v>
@@ -11064,62 +11072,62 @@
       </c>
       <c r="DW22" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="DX22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="DY22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="DZ22" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EA22" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EB22" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EC22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED22" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EE22" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF22" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EH22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI22" t="inlineStr">
@@ -11134,12 +11142,12 @@
       </c>
       <c r="EK22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EL22" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -11159,162 +11167,170 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>46099.4375</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>11</v>
+      </c>
+      <c r="T23" t="n">
         <v>8</v>
       </c>
-      <c r="L23" t="n">
-        <v>12</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="n">
-        <v>7</v>
-      </c>
       <c r="U23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V23" t="n">
         <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y23" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="Z23" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Jeonju World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
+        </is>
+      </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>4.65</v>
       </c>
       <c r="AH23" t="n">
         <v>1.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AJ23" t="n">
         <v>3.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB23" t="n">
-        <v>3836</v>
+        <v>3837</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11323,28 +11339,28 @@
         <v>-1</v>
       </c>
       <c r="BG23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH23" t="n">
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ23" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK23" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BL23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BM23" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN23" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO23" t="n">
         <v>1</v>
@@ -11353,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR23" t="n">
         <v>2</v>
@@ -11362,31 +11378,31 @@
         <v>1</v>
       </c>
       <c r="BT23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
       </c>
       <c r="BV23" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="BW23" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="BX23" t="n">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="BY23" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.21</v>
+        <v>3.12</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11413,16 +11429,16 @@
         <v>1</v>
       </c>
       <c r="CK23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL23" t="n">
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO23" t="n">
         <v>0</v>
@@ -11434,19 +11450,19 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CS23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
@@ -11458,154 +11474,2898 @@
         <v>6</v>
       </c>
       <c r="CZ23" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA23" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB23" t="n">
         <v>75</v>
       </c>
-      <c r="DA23" t="n">
+      <c r="DC23" t="n">
         <v>75</v>
       </c>
-      <c r="DB23" t="n">
+      <c r="DD23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ23" t="n">
         <v>50</v>
       </c>
-      <c r="DC23" t="n">
+      <c r="DK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU23" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW23" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr"/>
+      <c r="EJ23" t="inlineStr"/>
+      <c r="EK23" t="inlineStr"/>
+      <c r="EL23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46102.20833333334</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>8</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>9</v>
+      </c>
+      <c r="V24" t="n">
+        <v>11</v>
+      </c>
+      <c r="W24" t="n">
+        <v>11</v>
+      </c>
+      <c r="X24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Daejeon World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>3837</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>145</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP24" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW24" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DX24" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DY24" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="DZ24" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EA24" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EB24" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EC24" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED24" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE24" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EF24" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EG24" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EH24" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EI24" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ24" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EK24" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EL24" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46103.20833333334</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>10</v>
+      </c>
+      <c r="V25" t="n">
+        <v>4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>10</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Seoul World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>3833</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>25</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ25" t="n">
         <v>50</v>
       </c>
-      <c r="DD23" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DE23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF23" t="n">
+      <c r="DK25" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DO25" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT25" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU25" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV25" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW25" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DX25" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DY25" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="DZ25" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="EA25" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EB25" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EC25" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED25" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EE25" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF25" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EG25" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EH25" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EI25" t="inlineStr"/>
+      <c r="EJ25" t="inlineStr"/>
+      <c r="EK25" t="inlineStr"/>
+      <c r="EL25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46103.20833333334</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18</v>
+      </c>
+      <c r="V26" t="n">
+        <v>3</v>
+      </c>
+      <c r="W26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Ulsan Munsu Football Stadium</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>62</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>126</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DN26" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO26" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV26" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW26" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DX26" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="DY26" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="DZ26" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EA26" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EB26" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EE26" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EF26" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EG26" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr"/>
+      <c r="EJ26" t="inlineStr"/>
+      <c r="EK26" t="inlineStr"/>
+      <c r="EL26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>46103.3125</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>121</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>146</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>51</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ27" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC27" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE27" t="n">
         <v>0.5</v>
       </c>
-      <c r="DG23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH23" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DI23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DJ23" t="n">
+      <c r="DF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH27" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DM27" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DN27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW27" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>5.99</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EA27" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB27" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EE27" t="inlineStr"/>
+      <c r="EF27" t="inlineStr"/>
+      <c r="EG27" t="inlineStr"/>
+      <c r="EH27" t="inlineStr"/>
+      <c r="EI27" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ27" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EK27" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL27" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>46103.3125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>11</v>
+      </c>
+      <c r="W28" t="n">
+        <v>10</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG28" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK28" t="n">
         <v>25</v>
       </c>
-      <c r="DK23" t="n">
+      <c r="DL28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DM28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DN28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DO28" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW28" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="DX28" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="DY28" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="DZ28" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EA28" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EB28" t="inlineStr">
+        <is>
+          <t>5.58</t>
+        </is>
+      </c>
+      <c r="EC28" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="ED28" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EE28" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EF28" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG28" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EH28" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI28" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ28" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EK28" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EL28" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>46103.3125</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Anyang Stadium</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>3840</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ29" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA29" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB29" t="n">
         <v>25</v>
       </c>
-      <c r="DL23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="DM23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DN23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="DO23" t="n">
-        <v>3</v>
-      </c>
-      <c r="DP23" t="b">
-        <v>1</v>
-      </c>
-      <c r="DQ23" t="b">
-        <v>1</v>
-      </c>
-      <c r="DR23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV23" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW23" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="DX23" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="DY23" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="DZ23" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EA23" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="EB23" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EC23" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="ED23" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EE23" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EF23" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EH23" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EI23" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EJ23" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EK23" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EL23" t="inlineStr">
-        <is>
-          <t>2.99</t>
-        </is>
-      </c>
+      <c r="DC29" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF29" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DN29" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DO29" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW29" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DX29" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DY29" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="DZ29" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EA29" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EB29" t="inlineStr">
+        <is>
+          <t>4.97</t>
+        </is>
+      </c>
+      <c r="EC29" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="ED29" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EE29" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF29" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG29" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EH29" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI29" t="inlineStr"/>
+      <c r="EJ29" t="inlineStr"/>
+      <c r="EK29" t="inlineStr"/>
+      <c r="EL29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -11665,22 +11665,22 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S24" t="n">
         <v>6</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W24" t="n">
         <v>11</v>
@@ -11689,10 +11689,10 @@
         <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Z24" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -11852,13 +11852,13 @@
         <v>90</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="CA24" t="n">
         <v>1.65</v>
       </c>
       <c r="CB24" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="CC24" t="n">
         <v>0</v>
@@ -11903,31 +11903,31 @@
         <v>0</v>
       </c>
       <c r="CQ24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR24" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="CS24" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CT24" t="n">
         <v>1</v>
       </c>
       <c r="CU24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV24" t="n">
         <v>12</v>
       </c>
       <c r="CW24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX24" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY24" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ24" t="n">
         <v>0</v>
@@ -12137,22 +12137,22 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
+        <v>6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
         <v>7</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
       <c r="U25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
         <v>10</v>
@@ -12161,10 +12161,10 @@
         <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Z25" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -12324,13 +12324,13 @@
         <v>86</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CA25" t="n">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.13</v>
+        <v>2.43</v>
       </c>
       <c r="CC25" t="n">
         <v>0</v>
@@ -12375,31 +12375,31 @@
         <v>0</v>
       </c>
       <c r="CQ25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR25" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CS25" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CT25" t="n">
         <v>1</v>
       </c>
       <c r="CU25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV25" t="n">
         <v>13</v>
       </c>
       <c r="CW25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX25" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY25" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ25" t="n">
         <v>0</v>
@@ -12572,13 +12572,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12596,19 +12596,19 @@
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
         <v>9</v>
@@ -12617,10 +12617,10 @@
         <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Z26" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -12780,13 +12780,13 @@
         <v>126</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.73</v>
+        <v>1.23</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12831,13 +12831,13 @@
         <v>0</v>
       </c>
       <c r="CQ26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR26" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CS26" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CT26" t="n">
         <v>1</v>
@@ -12846,16 +12846,16 @@
         <v>21</v>
       </c>
       <c r="CV26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY26" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ26" t="n">
         <v>50</v>
@@ -13028,13 +13028,13 @@
         <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M27" t="n">
         <v>2</v>
@@ -13049,22 +13049,22 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
+        <v>16</v>
+      </c>
+      <c r="V27" t="n">
         <v>6</v>
-      </c>
-      <c r="V27" t="n">
-        <v>2</v>
       </c>
       <c r="W27" t="n">
         <v>3</v>
@@ -13073,10 +13073,10 @@
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
@@ -13228,13 +13228,13 @@
         <v>51</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.33</v>
+        <v>2.23</v>
       </c>
       <c r="CA27" t="n">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="CB27" t="n">
-        <v>1.82</v>
+        <v>2.97</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13279,13 +13279,13 @@
         <v>0</v>
       </c>
       <c r="CQ27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR27" t="n">
-        <v>-1</v>
+        <v>36</v>
       </c>
       <c r="CS27" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CT27" t="n">
         <v>1</v>
@@ -13294,16 +13294,16 @@
         <v>16</v>
       </c>
       <c r="CV27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CW27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY27" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CZ27" t="n">
         <v>50</v>
@@ -13479,10 +13479,10 @@
         <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
@@ -13497,22 +13497,22 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W28" t="n">
         <v>10</v>
@@ -13521,10 +13521,10 @@
         <v>9</v>
       </c>
       <c r="Y28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -13684,13 +13684,13 @@
         <v>107</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="CB28" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="CC28" t="n">
         <v>0</v>
@@ -13735,31 +13735,31 @@
         <v>0</v>
       </c>
       <c r="CQ28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR28" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CS28" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CT28" t="n">
         <v>1</v>
       </c>
       <c r="CU28" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV28" t="n">
         <v>11</v>
       </c>
-      <c r="CV28" t="n">
-        <v>13</v>
-      </c>
       <c r="CW28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX28" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CY28" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CZ28" t="n">
         <v>50</v>
@@ -13951,10 +13951,10 @@
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
         <v>4</v>
@@ -13969,22 +13969,22 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="W29" t="n">
         <v>15</v>
@@ -13993,10 +13993,10 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Z29" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -14156,13 +14156,13 @@
         <v>106</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0.35</v>
+        <v>0.67</v>
       </c>
       <c r="CA29" t="n">
-        <v>0.59</v>
+        <v>1.17</v>
       </c>
       <c r="CB29" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="CC29" t="n">
         <v>0</v>
@@ -14207,31 +14207,31 @@
         <v>0</v>
       </c>
       <c r="CQ29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR29" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="CS29" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CT29" t="n">
         <v>1</v>
       </c>
       <c r="CU29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CV29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CW29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX29" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY29" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ29" t="n">
         <v>75</v>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL29" headerRowCount="1">
-  <autoFilter ref="A1:EL29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL30" headerRowCount="1">
+  <autoFilter ref="A1:EL30"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL29"/>
+  <dimension ref="A1:EL30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>2</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -8238,7 +8238,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DE16" t="n">
         <v>1.33</v>
@@ -8271,7 +8271,7 @@
         <v>2.35</v>
       </c>
       <c r="DO16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8727,7 +8727,7 @@
         <v>1.44</v>
       </c>
       <c r="DO17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9617,7 +9617,7 @@
         <v>0.67</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DF19" t="n">
         <v>0.5</v>
@@ -9647,7 +9647,7 @@
         <v>3.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP19" t="b">
         <v>0</v>
@@ -11014,7 +11014,7 @@
         <v>50</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DE22" t="n">
         <v>3</v>
@@ -13007,35 +13007,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>46103.3125</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
         <v>11</v>
       </c>
-      <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
-        <v>14</v>
-      </c>
       <c r="M27" t="n">
         <v>2</v>
       </c>
@@ -13043,13 +13043,13 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>2</v>
@@ -13058,102 +13058,110 @@
         <v>11</v>
       </c>
       <c r="T27" t="n">
+        <v>11</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11</v>
+      </c>
+      <c r="V27" t="n">
+        <v>13</v>
+      </c>
+      <c r="W27" t="n">
+        <v>10</v>
+      </c>
+      <c r="X27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
         <v>4</v>
       </c>
-      <c r="U27" t="n">
-        <v>16</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF27" t="n">
         <v>3</v>
       </c>
-      <c r="X27" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AG27" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.57</v>
+        <v>3.02</v>
       </c>
       <c r="AO27" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AR27" t="n">
-        <v>3.22</v>
+        <v>3.39</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AU27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
         <v>-1</v>
@@ -13162,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BE27" t="n">
         <v>0</v>
@@ -13201,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR27" t="n">
         <v>1</v>
@@ -13210,31 +13218,31 @@
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU27" t="n">
         <v>1</v>
       </c>
       <c r="BV27" t="n">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="BW27" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="BX27" t="n">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="BY27" t="n">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="BZ27" t="n">
-        <v>2.23</v>
+        <v>0.91</v>
       </c>
       <c r="CA27" t="n">
-        <v>0.74</v>
+        <v>1.34</v>
       </c>
       <c r="CB27" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13282,82 +13290,82 @@
         <v>1</v>
       </c>
       <c r="CR27" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="CS27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CT27" t="n">
         <v>1</v>
       </c>
       <c r="CU27" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="CV27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CW27" t="n">
         <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CY27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="CZ27" t="n">
         <v>50</v>
       </c>
       <c r="DA27" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB27" t="n">
         <v>50</v>
       </c>
       <c r="DC27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF27" t="n">
         <v>0.5</v>
       </c>
-      <c r="DF27" t="n">
-        <v>1</v>
-      </c>
       <c r="DG27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH27" t="n">
         <v>0.67</v>
       </c>
       <c r="DI27" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="DJ27" t="n">
         <v>50</v>
       </c>
       <c r="DK27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL27" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="DM27" t="n">
-        <v>0.76</v>
+        <v>1.09</v>
       </c>
       <c r="DN27" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="DO27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR27" t="b">
         <v>0</v>
@@ -13372,52 +13380,68 @@
         <v>0</v>
       </c>
       <c r="DV27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW27" t="inlineStr">
         <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EA27" t="inlineStr">
+        <is>
           <t>2.23</t>
         </is>
       </c>
-      <c r="DX27" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="DY27" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="DZ27" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="EA27" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="EC27" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="ED27" t="inlineStr">
         <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="EE27" t="inlineStr"/>
-      <c r="EF27" t="inlineStr"/>
-      <c r="EG27" t="inlineStr"/>
-      <c r="EH27" t="inlineStr"/>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EE27" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EF27" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG27" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
       <c r="EI27" t="inlineStr">
         <is>
           <t>1.34</t>
@@ -13425,17 +13449,17 @@
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL27" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.29</t>
         </is>
       </c>
     </row>
@@ -13455,12 +13479,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -13470,128 +13494,128 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
         <v>7</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
+        <v>9</v>
+      </c>
+      <c r="M28" t="n">
         <v>4</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
+      </c>
+      <c r="V28" t="n">
         <v>11</v>
       </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>11</v>
-      </c>
-      <c r="T28" t="n">
-        <v>11</v>
-      </c>
-      <c r="U28" t="n">
-        <v>11</v>
-      </c>
-      <c r="V28" t="n">
-        <v>13</v>
-      </c>
       <c r="W28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Z28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Steelyard Stadium</t>
+          <t>Anyang Stadium</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>, Pohang</t>
+          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
         </is>
       </c>
       <c r="AC28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" t="n">
         <v>2.3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AN28" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -13603,22 +13627,22 @@
         <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>-1</v>
+        <v>3840</v>
       </c>
       <c r="BC28" t="n">
         <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BE28" t="n">
         <v>0</v>
@@ -13627,31 +13651,31 @@
         <v>-1</v>
       </c>
       <c r="BG28" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH28" t="n">
         <v>1</v>
       </c>
       <c r="BI28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK28" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL28" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BM28" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN28" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP28" t="n">
         <v>0</v>
@@ -13660,157 +13684,157 @@
         <v>2</v>
       </c>
       <c r="BR28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX28" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY28" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ28" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA28" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC28" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF28" t="n">
         <v>3</v>
       </c>
-      <c r="BU28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>51</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>109</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>107</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CA28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CB28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS28" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU28" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV28" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX28" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ28" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA28" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB28" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC28" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD28" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DE28" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF28" t="n">
+      <c r="DG28" t="n">
         <v>0.5</v>
       </c>
-      <c r="DG28" t="n">
-        <v>3</v>
-      </c>
       <c r="DH28" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="DI28" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="DJ28" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL28" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DM28" t="n">
-        <v>1.09</v>
+        <v>1.87</v>
       </c>
       <c r="DN28" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
       <c r="DO28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ28" t="b">
         <v>0</v>
@@ -13832,84 +13856,68 @@
       </c>
       <c r="DW28" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DX28" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="DY28" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DZ28" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EA28" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB28" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="EC28" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="ED28" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EE28" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF28" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EG28" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EH28" t="inlineStr">
         <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EI28" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EJ28" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EK28" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EL28" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EI28" t="inlineStr"/>
+      <c r="EJ28" t="inlineStr"/>
+      <c r="EK28" t="inlineStr"/>
+      <c r="EL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13927,164 +13935,156 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
         <v>46103.3125</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="n">
         <v>4</v>
       </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
+        <v>16</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6</v>
+      </c>
+      <c r="W29" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>6</v>
-      </c>
-      <c r="V29" t="n">
-        <v>11</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>15</v>
       </c>
-      <c r="X29" t="n">
-        <v>5</v>
-      </c>
       <c r="Y29" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="Z29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.58</v>
+        <v>5.2</v>
       </c>
       <c r="AH29" t="n">
         <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.49</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AS29" t="n">
         <v>2.44</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV29" t="n">
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
         <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB29" t="n">
-        <v>3840</v>
+        <v>-1</v>
       </c>
       <c r="BC29" t="n">
         <v>0</v>
@@ -14099,184 +14099,184 @@
         <v>-1</v>
       </c>
       <c r="BG29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH29" t="n">
         <v>1</v>
       </c>
       <c r="BI29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BK29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL29" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>121</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>146</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>51</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB29" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>36</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX29" t="n">
         <v>3</v>
       </c>
-      <c r="BN29" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS29" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT29" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU29" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV29" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW29" t="n">
-        <v>35</v>
-      </c>
-      <c r="BX29" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY29" t="n">
-        <v>106</v>
-      </c>
-      <c r="BZ29" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="CA29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CB29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS29" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU29" t="n">
-        <v>6</v>
-      </c>
-      <c r="CV29" t="n">
+      <c r="CY29" t="n">
         <v>15</v>
       </c>
-      <c r="CW29" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX29" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY29" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ29" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DA29" t="n">
         <v>100</v>
       </c>
       <c r="DB29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DC29" t="n">
         <v>50</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DG29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DH29" t="n">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="DI29" t="n">
         <v>0.25</v>
       </c>
       <c r="DJ29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DK29" t="n">
         <v>0</v>
       </c>
       <c r="DL29" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DM29" t="n">
-        <v>1.87</v>
+        <v>0.76</v>
       </c>
       <c r="DN29" t="n">
-        <v>3.43</v>
+        <v>2.46</v>
       </c>
       <c r="DO29" t="n">
         <v>5</v>
@@ -14285,7 +14285,7 @@
         <v>1</v>
       </c>
       <c r="DQ29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR29" t="b">
         <v>0</v>
@@ -14300,72 +14300,536 @@
         <v>0</v>
       </c>
       <c r="DV29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW29" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="DX29" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="DY29" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="DZ29" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EA29" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EB29" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="EC29" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="ED29" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EE29" t="inlineStr"/>
+      <c r="EF29" t="inlineStr"/>
+      <c r="EG29" t="inlineStr"/>
+      <c r="EH29" t="inlineStr"/>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>46109.25</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>3835</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>22</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>42</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>59</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW30" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="DX30" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="DY30" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="DZ30" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EA30" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EB30" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="EC30" t="inlineStr">
+        <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="ED29" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EE29" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF29" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EG29" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EH29" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EI29" t="inlineStr"/>
-      <c r="EJ29" t="inlineStr"/>
-      <c r="EK29" t="inlineStr"/>
-      <c r="EL29" t="inlineStr"/>
+      <c r="ED30" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EE30" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EF30" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EG30" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH30" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI30" t="inlineStr"/>
+      <c r="EJ30" t="inlineStr"/>
+      <c r="EK30" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EL30" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -1506,13 +1506,13 @@
         <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
         <v>14</v>
@@ -1687,10 +1687,10 @@
         <v>1.02</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="CC2" t="n">
         <v>1</v>
@@ -1962,13 +1962,13 @@
         <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
         <v>11</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
         <v>10</v>
@@ -2143,10 +2143,10 @@
         <v>1.4</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -2913,10 +2913,10 @@
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
@@ -3370,13 +3370,13 @@
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6" t="n">
         <v>11</v>
@@ -3540,13 +3540,13 @@
         <v>107</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -4725,7 +4725,7 @@
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>4</v>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>4</v>
@@ -4897,7 +4897,7 @@
         <v>2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR9" t="n">
         <v>2</v>
@@ -4906,7 +4906,7 @@
         <v>2</v>
       </c>
       <c r="BT9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU9" t="n">
         <v>1</v>
@@ -5189,7 +5189,7 @@
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
@@ -5233,7 +5233,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
         <v>1</v>
@@ -5362,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU10" t="n">
         <v>1</v>
@@ -6125,7 +6125,7 @@
         <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
         <v>5</v>
@@ -6149,7 +6149,7 @@
         <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
         <v>17</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
         <v>3</v>
@@ -6291,7 +6291,7 @@
         <v>6</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
         <v>1</v>
@@ -6303,7 +6303,7 @@
         <v>2</v>
       </c>
       <c r="BS12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT12" t="n">
         <v>4</v>
@@ -6324,13 +6324,13 @@
         <v>101</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="CA12" t="n">
         <v>2</v>
       </c>
       <c r="CB12" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP12" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
         <v>3</v>
@@ -6613,7 +6613,7 @@
         <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V13" t="n">
         <v>10</v>
@@ -6625,10 +6625,10 @@
         <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -6788,13 +6788,13 @@
         <v>93</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="CA13" t="n">
         <v>1.17</v>
       </c>
       <c r="CB13" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -7806,13 +7806,13 @@
         <v>50</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="DM15" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DN15" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="DO15" t="n">
         <v>4</v>
@@ -9169,10 +9169,10 @@
         <v>1.34</v>
       </c>
       <c r="DM18" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="DN18" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="DO18" t="n">
         <v>5</v>
@@ -9641,10 +9641,10 @@
         <v>1.22</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="DN19" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="DO19" t="n">
         <v>5</v>
@@ -9931,28 +9931,28 @@
         <v>-1</v>
       </c>
       <c r="BG20" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH20" t="n">
         <v>1</v>
       </c>
       <c r="BI20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK20" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BL20" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BM20" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN20" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BO20" t="n">
         <v>1</v>
@@ -10027,10 +10027,10 @@
         <v>0</v>
       </c>
       <c r="CM20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
@@ -10102,13 +10102,13 @@
         <v>25</v>
       </c>
       <c r="DL20" t="n">
-        <v>1.05</v>
+        <v>0.98</v>
       </c>
       <c r="DM20" t="n">
         <v>2.15</v>
       </c>
       <c r="DN20" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="DO20" t="n">
         <v>4</v>
@@ -10867,28 +10867,28 @@
         <v>-1</v>
       </c>
       <c r="BG22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH22" t="n">
         <v>1</v>
       </c>
       <c r="BI22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BL22" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BM22" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN22" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO22" t="n">
         <v>2</v>
@@ -10963,10 +10963,10 @@
         <v>1</v>
       </c>
       <c r="CM22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO22" t="n">
         <v>0</v>
@@ -11041,10 +11041,10 @@
         <v>1.22</v>
       </c>
       <c r="DM22" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DN22" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="DO22" t="n">
         <v>4</v>
@@ -11197,10 +11197,10 @@
         <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>1.74</v>
@@ -11369,16 +11369,16 @@
         <v>0</v>
       </c>
       <c r="BQ23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS23" t="n">
         <v>1</v>
       </c>
       <c r="BT23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
         <v>7</v>
@@ -11677,7 +11677,7 @@
         <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>12</v>
@@ -11852,13 +11852,13 @@
         <v>90</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="CA24" t="n">
         <v>1.65</v>
       </c>
       <c r="CB24" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="CC24" t="n">
         <v>0</v>
@@ -11966,13 +11966,13 @@
         <v>25</v>
       </c>
       <c r="DL24" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DM24" t="n">
         <v>1.46</v>
       </c>
       <c r="DN24" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="DO24" t="n">
         <v>5</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="DM25" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DN25" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DO25" t="n">
         <v>4</v>
@@ -12596,13 +12596,13 @@
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
       </c>
       <c r="T26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26" t="n">
         <v>19</v>
@@ -12723,28 +12723,28 @@
         <v>-1</v>
       </c>
       <c r="BG26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BK26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM26" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN26" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO26" t="n">
         <v>0</v>
@@ -12783,10 +12783,10 @@
         <v>1.99</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="CB26" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12819,10 +12819,10 @@
         <v>0</v>
       </c>
       <c r="CM26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CN26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -13179,28 +13179,28 @@
         <v>-1</v>
       </c>
       <c r="BG27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH27" t="n">
         <v>1</v>
       </c>
       <c r="BI27" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK27" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BL27" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BM27" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN27" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO27" t="n">
         <v>1</v>
@@ -13275,10 +13275,10 @@
         <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CN27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO27" t="n">
         <v>0</v>
@@ -13530,13 +13530,13 @@
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28" t="n">
         <v>6</v>
       </c>
       <c r="V28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
         <v>15</v>
@@ -13651,28 +13651,28 @@
         <v>-1</v>
       </c>
       <c r="BG28" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH28" t="n">
         <v>1</v>
       </c>
       <c r="BI28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ28" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BK28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL28" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BM28" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BN28" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BO28" t="n">
         <v>3</v>
@@ -13711,10 +13711,10 @@
         <v>0.67</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="CB28" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="CC28" t="n">
         <v>0</v>
@@ -13747,10 +13747,10 @@
         <v>0</v>
       </c>
       <c r="CM28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CN28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO28" t="n">
         <v>0</v>
@@ -14099,28 +14099,28 @@
         <v>-1</v>
       </c>
       <c r="BG29" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH29" t="n">
         <v>1</v>
       </c>
       <c r="BI29" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BJ29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK29" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BL29" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM29" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BN29" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BO29" t="n">
         <v>1</v>
@@ -14195,10 +14195,10 @@
         <v>0</v>
       </c>
       <c r="CM29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CO29" t="n">
         <v>0</v>
@@ -14425,22 +14425,22 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
         <v>8</v>
@@ -14449,10 +14449,10 @@
         <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z30" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -14612,13 +14612,13 @@
         <v>101</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0.89</v>
+        <v>1.86</v>
       </c>
       <c r="CA30" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="CB30" t="n">
-        <v>1.63</v>
+        <v>2.85</v>
       </c>
       <c r="CC30" t="n">
         <v>0</v>
@@ -14663,31 +14663,31 @@
         <v>0</v>
       </c>
       <c r="CQ30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR30" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="CS30" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="CT30" t="n">
         <v>1</v>
       </c>
       <c r="CU30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CV30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CW30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX30" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY30" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ30" t="n">
         <v>25</v>
@@ -14729,10 +14729,10 @@
         <v>1.18</v>
       </c>
       <c r="DM30" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="DN30" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DO30" t="n">
         <v>5</v>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -14892,19 +14892,19 @@
         <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W31" t="n">
         <v>12</v>
@@ -14913,10 +14913,10 @@
         <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Z31" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -15076,13 +15076,13 @@
         <v>95</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="CB31" t="n">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="CC31" t="n">
         <v>0</v>
@@ -15127,13 +15127,13 @@
         <v>0</v>
       </c>
       <c r="CQ31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR31" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CS31" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CT31" t="n">
         <v>1</v>
@@ -15142,16 +15142,16 @@
         <v>10</v>
       </c>
       <c r="CV31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX31" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CY31" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ31" t="n">
         <v>75</v>
@@ -15353,34 +15353,34 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32" t="n">
         <v>4</v>
       </c>
       <c r="W32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Z32" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
@@ -15532,13 +15532,13 @@
         <v>99</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CA32" t="n">
         <v>0.63</v>
       </c>
       <c r="CB32" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CC32" t="n">
         <v>0</v>
@@ -15583,31 +15583,31 @@
         <v>0</v>
       </c>
       <c r="CQ32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR32" t="n">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="CS32" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CT32" t="n">
         <v>1</v>
       </c>
       <c r="CU32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX32" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY32" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CZ32" t="n">
         <v>42</v>
@@ -15799,16 +15799,16 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
         <v>23</v>
@@ -15817,10 +15817,10 @@
         <v>16</v>
       </c>
       <c r="Y33" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="Z33" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -15980,13 +15980,13 @@
         <v>63</v>
       </c>
       <c r="BZ33" t="n">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -16031,13 +16031,13 @@
         <v>0</v>
       </c>
       <c r="CQ33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CS33" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="CT33" t="n">
         <v>1</v>
@@ -16046,16 +16046,16 @@
         <v>16</v>
       </c>
       <c r="CV33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CW33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CY33" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CZ33" t="n">
         <v>17</v>
@@ -16255,22 +16255,22 @@
         <v>3</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W34" t="n">
+        <v>15</v>
+      </c>
+      <c r="X34" t="n">
         <v>14</v>
-      </c>
-      <c r="X34" t="n">
-        <v>13</v>
       </c>
       <c r="Y34" t="n">
         <v>68</v>
@@ -16436,13 +16436,13 @@
         <v>89</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="CA34" t="n">
-        <v>0.87</v>
+        <v>1.18</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.21</v>
+        <v>2.89</v>
       </c>
       <c r="CC34" t="n">
         <v>1</v>
@@ -16487,13 +16487,13 @@
         <v>0</v>
       </c>
       <c r="CQ34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CS34" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
@@ -16505,13 +16505,13 @@
         <v>16</v>
       </c>
       <c r="CW34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY34" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ34" t="n">
         <v>25</v>
@@ -16701,10 +16701,10 @@
         <v>13</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -16713,34 +16713,34 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W35" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="X35" t="n">
         <v>19</v>
       </c>
       <c r="Y35" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Z35" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
         <v>3.75</v>
@@ -16840,7 +16840,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>-1</v>
+        <v>11542</v>
       </c>
       <c r="BG35" t="n">
         <v>2</v>
@@ -16873,16 +16873,16 @@
         <v>0</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS35" t="n">
         <v>1</v>
       </c>
       <c r="BT35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU35" t="n">
         <v>1</v>
@@ -16900,13 +16900,13 @@
         <v>98</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0.75</v>
+        <v>1.01</v>
       </c>
       <c r="CA35" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.32</v>
+        <v>2.22</v>
       </c>
       <c r="CC35" t="n">
         <v>0</v>
@@ -16951,13 +16951,13 @@
         <v>0</v>
       </c>
       <c r="CQ35" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="CS35" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
@@ -16966,16 +16966,16 @@
         <v>19</v>
       </c>
       <c r="CV35" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CW35" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX35" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY35" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ35" t="n">
         <v>59</v>
@@ -17161,22 +17161,22 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
         <v>8</v>
@@ -17185,10 +17185,10 @@
         <v>19</v>
       </c>
       <c r="Y36" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="Z36" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>8239</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -17318,19 +17318,19 @@
         <v>0</v>
       </c>
       <c r="BP36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ36" t="n">
         <v>1</v>
       </c>
       <c r="BR36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU36" t="n">
         <v>1</v>
@@ -17348,13 +17348,13 @@
         <v>107</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0.9</v>
+        <v>1.66</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="CB36" t="n">
-        <v>1.77</v>
+        <v>2.79</v>
       </c>
       <c r="CC36" t="n">
         <v>1</v>
@@ -17381,7 +17381,7 @@
         <v>1</v>
       </c>
       <c r="CK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL36" t="n">
         <v>0</v>
@@ -17399,31 +17399,31 @@
         <v>0</v>
       </c>
       <c r="CQ36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR36" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CS36" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="CT36" t="n">
         <v>1</v>
       </c>
       <c r="CU36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CV36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CW36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX36" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY36" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ36" t="n">
         <v>50</v>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL36" headerRowCount="1">
-  <autoFilter ref="A1:EL36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL42" headerRowCount="1">
+  <autoFilter ref="A1:EL42"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL36"/>
+  <dimension ref="A1:EL42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DE2" t="n">
         <v>2.5</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>2</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3169,7 +3169,7 @@
         <v>2</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP6" t="b">
         <v>0</v>
@@ -4102,10 +4102,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4558,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DE8" t="n">
         <v>1.33</v>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5473,7 +5473,7 @@
         <v>1</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -5503,7 +5503,7 @@
         <v>1.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5945,7 +5945,7 @@
         <v>1.33</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5975,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6414,10 +6414,10 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="DF12" t="n">
         <v>3</v>
@@ -6447,7 +6447,7 @@
         <v>1.94</v>
       </c>
       <c r="DO12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP12" t="b">
         <v>0</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DE13" t="n">
         <v>0.67</v>
@@ -6911,7 +6911,7 @@
         <v>1.93</v>
       </c>
       <c r="DO13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -7020,19 +7020,19 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7044,111 +7044,119 @@
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Z14" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Bucheon Stadium</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+        </is>
+      </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="AF14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3.1</v>
       </c>
-      <c r="AG14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AS14" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3833</v>
+        <v>3836</v>
       </c>
       <c r="BC14" t="n">
         <v>0</v>
@@ -7160,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>7518</v>
+        <v>-1</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -7169,76 +7177,76 @@
         <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
         <v>6</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BN14" t="n">
         <v>3</v>
       </c>
-      <c r="BN14" t="n">
-        <v>7</v>
-      </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU14" t="n">
         <v>1</v>
       </c>
       <c r="BV14" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="BW14" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="BX14" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="BY14" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="CB14" t="n">
-        <v>3</v>
+        <v>3.51</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG14" t="n">
         <v>0</v>
@@ -7253,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="CK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -7262,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
@@ -7277,7 +7285,7 @@
         <v>18</v>
       </c>
       <c r="CS14" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="CT14" t="n">
         <v>1</v>
@@ -7286,7 +7294,7 @@
         <v>13</v>
       </c>
       <c r="CV14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CW14" t="n">
         <v>1</v>
@@ -7295,10 +7303,10 @@
         <v>8</v>
       </c>
       <c r="CY14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CZ14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA14" t="n">
         <v>50</v>
@@ -7310,19 +7318,19 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="DF14" t="n">
         <v>1</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI14" t="n">
         <v>3</v>
@@ -7331,19 +7339,19 @@
         <v>50</v>
       </c>
       <c r="DK14" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="DM14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>2.38</v>
+        <v>1.08</v>
       </c>
       <c r="DO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7368,7 +7376,7 @@
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
@@ -7378,58 +7386,74 @@
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="DZ14" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EA14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EB14" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EC14" t="inlineStr">
         <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr"/>
-      <c r="EJ14" t="inlineStr"/>
-      <c r="EK14" t="inlineStr"/>
-      <c r="EL14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7447,12 +7471,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -7468,20 +7492,20 @@
         <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>9</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
@@ -7492,119 +7516,111 @@
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="X15" t="n">
         <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="AF15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>3.3</v>
       </c>
-      <c r="AG15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
         <v>3</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>3836</v>
+        <v>3833</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
@@ -7616,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>7518</v>
       </c>
       <c r="BG15" t="n">
         <v>2</v>
@@ -7625,76 +7641,76 @@
         <v>1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM15" t="n">
         <v>3</v>
       </c>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>6</v>
-      </c>
       <c r="BN15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
         <v>3</v>
       </c>
-      <c r="BO15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>0</v>
-      </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU15" t="n">
         <v>1</v>
       </c>
       <c r="BV15" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="BW15" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="BX15" t="n">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="BY15" t="n">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.51</v>
+        <v>3</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
         <v>0</v>
       </c>
       <c r="CF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
         <v>0</v>
@@ -7709,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="CK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -7718,7 +7734,7 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
@@ -7733,7 +7749,7 @@
         <v>18</v>
       </c>
       <c r="CS15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="CT15" t="n">
         <v>1</v>
@@ -7742,7 +7758,7 @@
         <v>13</v>
       </c>
       <c r="CV15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CW15" t="n">
         <v>1</v>
@@ -7751,10 +7767,10 @@
         <v>8</v>
       </c>
       <c r="CY15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA15" t="n">
         <v>50</v>
@@ -7766,19 +7782,19 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH15" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DI15" t="n">
         <v>3</v>
@@ -7787,19 +7803,19 @@
         <v>50</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.08</v>
+        <v>2.38</v>
       </c>
       <c r="DO15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7824,7 +7840,7 @@
       </c>
       <c r="DW15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="DX15" t="inlineStr">
@@ -7834,74 +7850,58 @@
       </c>
       <c r="DY15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="DZ15" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EA15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EB15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EC15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="ED15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EE15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EF15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EG15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EH15" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI15" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EJ15" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="EK15" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EL15" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr"/>
+      <c r="EL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -7940,132 +7940,140 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
+        <v>12</v>
+      </c>
+      <c r="X16" t="n">
         <v>9</v>
       </c>
-      <c r="X16" t="n">
-        <v>7</v>
-      </c>
       <c r="Y16" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="Z16" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="n">
         <v>-1</v>
@@ -8089,64 +8097,64 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM16" t="n">
         <v>3</v>
       </c>
-      <c r="BK16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>8</v>
-      </c>
       <c r="BN16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="BO16" t="n">
         <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR16" t="n">
         <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="BW16" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="BX16" t="n">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="BY16" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.87</v>
+        <v>1.39</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8173,16 +8181,16 @@
         <v>1</v>
       </c>
       <c r="CK16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8194,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="CS16" t="n">
         <v>14</v>
@@ -8203,52 +8211,52 @@
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA16" t="n">
         <v>50</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -8257,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="DO16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8288,66 +8296,74 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr"/>
-      <c r="EF16" t="inlineStr"/>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
       <c r="EG16" t="inlineStr"/>
       <c r="EH16" t="inlineStr"/>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8383,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8388,140 +8404,132 @@
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>4</v>
       </c>
       <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
+        <v>14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9</v>
+      </c>
+      <c r="X17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>4</v>
       </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.92</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.36</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AU17" t="n">
         <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
         <v>-1</v>
@@ -8545,64 +8553,64 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BO17" t="n">
         <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
         <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="BW17" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="BX17" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="BY17" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.39</v>
+        <v>0.87</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8629,16 +8637,16 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8650,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="CS17" t="n">
         <v>14</v>
@@ -8659,53 +8667,53 @@
         <v>1</v>
       </c>
       <c r="CU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV17" t="n">
         <v>9</v>
       </c>
-      <c r="CV17" t="n">
-        <v>13</v>
-      </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="CZ17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA17" t="n">
         <v>50</v>
       </c>
       <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ17" t="n">
         <v>50</v>
       </c>
-      <c r="DC17" t="n">
-        <v>50</v>
-      </c>
-      <c r="DD17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>0</v>
-      </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
@@ -8713,13 +8721,13 @@
         <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="DO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -8744,74 +8752,66 @@
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EE17" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr"/>
+      <c r="EF17" t="inlineStr"/>
       <c r="EG17" t="inlineStr"/>
       <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.46</t>
         </is>
       </c>
     </row>
@@ -9175,7 +9175,7 @@
         <v>2.48</v>
       </c>
       <c r="DO18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9295,37 +9295,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>46099.4375</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" t="n">
         <v>3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
@@ -9337,122 +9337,122 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
         <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10</v>
+      </c>
+      <c r="V19" t="n">
         <v>8</v>
       </c>
-      <c r="U19" t="n">
-        <v>9</v>
-      </c>
-      <c r="V19" t="n">
-        <v>10</v>
-      </c>
       <c r="W19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X19" t="n">
         <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Z19" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bucheon Stadium</t>
+          <t>Sungui Arena Park</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+          <t>Dowon-dong, Jung-gu, Incheon</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
         <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR19" t="n">
         <v>3.1</v>
       </c>
-      <c r="AG19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AS19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU19" t="n">
         <v>4</v>
       </c>
-      <c r="AK19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1</v>
+        <v>3845</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -9473,64 +9473,64 @@
         <v>1</v>
       </c>
       <c r="BI19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL19" t="n">
         <v>1</v>
       </c>
       <c r="BM19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN19" t="n">
         <v>3</v>
       </c>
-      <c r="BN19" t="n">
-        <v>2</v>
-      </c>
       <c r="BO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS19" t="n">
         <v>2</v>
       </c>
       <c r="BT19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU19" t="n">
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW19" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="BX19" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="BY19" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CB19" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -9560,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
@@ -9578,88 +9578,88 @@
         <v>1</v>
       </c>
       <c r="CR19" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="CS19" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT19" t="n">
         <v>1</v>
       </c>
       <c r="CU19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CW19" t="n">
         <v>1</v>
       </c>
       <c r="CX19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="CY19" t="n">
         <v>2</v>
       </c>
       <c r="CZ19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DA19" t="n">
         <v>100</v>
       </c>
       <c r="DB19" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DC19" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DE19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH19" t="n">
         <v>0.33</v>
       </c>
-      <c r="DF19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="DI19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DK19" t="n">
         <v>0</v>
       </c>
       <c r="DL19" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="DM19" t="n">
-        <v>1.82</v>
+        <v>1.54</v>
       </c>
       <c r="DN19" t="n">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="DO19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT19" t="b">
         <v>0</v>
@@ -9668,86 +9668,78 @@
         <v>0</v>
       </c>
       <c r="DV19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW19" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DX19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="DY19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DZ19" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EA19" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB19" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="EC19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EE19" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF19" t="inlineStr">
         <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EG19" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EH19" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
       <c r="EI19" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ19" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EK19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EL19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -9767,12 +9759,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -9782,134 +9774,134 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
         <v>4</v>
       </c>
-      <c r="K20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" t="n">
         <v>10</v>
       </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="W20" t="n">
+        <v>13</v>
+      </c>
+      <c r="X20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Bucheon Stadium</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>4</v>
       </c>
-      <c r="R20" t="n">
-        <v>4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>13</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>15</v>
-      </c>
-      <c r="X20" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
-      <c r="AC20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.28</v>
+        <v>2.82</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AR20" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -9921,10 +9913,10 @@
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>3833</v>
+        <v>-1</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -9945,64 +9937,64 @@
         <v>1</v>
       </c>
       <c r="BI20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM20" t="n">
         <v>3</v>
       </c>
-      <c r="BK20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>5</v>
-      </c>
       <c r="BN20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS20" t="n">
         <v>2</v>
       </c>
       <c r="BT20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="BW20" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="BX20" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="BY20" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -10032,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
@@ -10050,61 +10042,61 @@
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="CS20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="CV20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CY20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CZ20" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DA20" t="n">
         <v>100</v>
       </c>
       <c r="DB20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="DC20" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="DF20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DG20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DI20" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DJ20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK20" t="n">
         <v>0</v>
@@ -10113,16 +10105,16 @@
         <v>1.22</v>
       </c>
       <c r="DM20" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="DN20" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="DO20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="DP20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ20" t="b">
         <v>0</v>
@@ -10144,62 +10136,62 @@
       </c>
       <c r="DW20" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DX20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="DY20" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="DZ20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="EA20" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="EB20" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="EC20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="ED20" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EE20" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EG20" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EH20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EI20" t="inlineStr">
@@ -10214,12 +10206,12 @@
       </c>
       <c r="EK20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL20" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.64</t>
         </is>
       </c>
     </row>
@@ -10239,149 +10231,141 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>46099.4375</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>7</v>
       </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>9</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="Z21" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>4.05</v>
+        <v>3.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -10393,16 +10377,16 @@
         <v>2</v>
       </c>
       <c r="BA21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>3845</v>
+        <v>3836</v>
       </c>
       <c r="BC21" t="n">
         <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BE21" t="n">
         <v>0</v>
@@ -10417,64 +10401,64 @@
         <v>1</v>
       </c>
       <c r="BI21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BJ21" t="n">
         <v>1</v>
       </c>
       <c r="BK21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BM21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BN21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT21" t="n">
         <v>3</v>
       </c>
-      <c r="BO21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>4</v>
-      </c>
       <c r="BU21" t="n">
         <v>1</v>
       </c>
       <c r="BV21" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BW21" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="BX21" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="BY21" t="n">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="CC21" t="n">
         <v>0</v>
@@ -10504,7 +10488,7 @@
         <v>0</v>
       </c>
       <c r="CL21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM21" t="n">
         <v>0</v>
@@ -10525,70 +10509,70 @@
         <v>18</v>
       </c>
       <c r="CS21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CT21" t="n">
         <v>1</v>
       </c>
       <c r="CU21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CV21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CW21" t="n">
         <v>1</v>
       </c>
       <c r="CX21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CY21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ21" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB21" t="n">
         <v>50</v>
       </c>
-      <c r="DA21" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB21" t="n">
-        <v>0</v>
-      </c>
       <c r="DC21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD21" t="n">
         <v>1</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="DF21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DG21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH21" t="n">
         <v>0.33</v>
       </c>
       <c r="DI21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DJ21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DK21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL21" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="DM21" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="DN21" t="n">
-        <v>2.56</v>
+        <v>3.13</v>
       </c>
       <c r="DO21" t="n">
         <v>6</v>
@@ -10600,10 +10584,10 @@
         <v>1</v>
       </c>
       <c r="DR21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT21" t="b">
         <v>0</v>
@@ -10612,78 +10596,86 @@
         <v>0</v>
       </c>
       <c r="DV21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="DX21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="DY21" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DZ21" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EA21" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="EB21" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EC21" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="ED21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EE21" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EF21" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EG21" t="inlineStr"/>
-      <c r="EH21" t="inlineStr"/>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EG21" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EH21" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
       <c r="EI21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EJ21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EK21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EL21" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.99</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11017,7 @@
         <v>2</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11055,7 +11047,7 @@
         <v>2.71</v>
       </c>
       <c r="DO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11159,12 +11151,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -11174,147 +11166,155 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
         <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>13</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>15</v>
+      </c>
+      <c r="X23" t="n">
         <v>7</v>
       </c>
-      <c r="U23" t="n">
-        <v>17</v>
-      </c>
-      <c r="V23" t="n">
-        <v>11</v>
-      </c>
-      <c r="W23" t="n">
-        <v>11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>12</v>
-      </c>
       <c r="Y23" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Z23" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.04</v>
+        <v>3.28</v>
       </c>
       <c r="AO23" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB23" t="n">
-        <v>3836</v>
+        <v>3833</v>
       </c>
       <c r="BC23" t="n">
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="BE23" t="n">
         <v>0</v>
@@ -11329,64 +11329,64 @@
         <v>1</v>
       </c>
       <c r="BI23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL23" t="n">
         <v>3</v>
       </c>
-      <c r="BL23" t="n">
-        <v>7</v>
-      </c>
       <c r="BM23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BN23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BO23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP23" t="n">
         <v>0</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BR23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU23" t="n">
         <v>1</v>
       </c>
       <c r="BV23" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="BW23" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="BX23" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="BY23" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="CB23" t="n">
-        <v>3.21</v>
+        <v>2.6</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -11416,7 +11416,7 @@
         <v>0</v>
       </c>
       <c r="CL23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM23" t="n">
         <v>0</v>
@@ -11434,19 +11434,19 @@
         <v>1</v>
       </c>
       <c r="CR23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CS23" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="CT23" t="n">
         <v>1</v>
       </c>
       <c r="CU23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CV23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW23" t="n">
         <v>1</v>
@@ -11455,61 +11455,61 @@
         <v>7</v>
       </c>
       <c r="CY23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ23" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DA23" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC23" t="n">
         <v>50</v>
       </c>
       <c r="DD23" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DE23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DF23" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DG23" t="n">
         <v>3</v>
       </c>
       <c r="DH23" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DI23" t="n">
         <v>3</v>
       </c>
       <c r="DJ23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DK23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="DM23" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="DN23" t="n">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="DO23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
       </c>
       <c r="DQ23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR23" t="b">
         <v>0</v>
@@ -11528,82 +11528,82 @@
       </c>
       <c r="DW23" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="DX23" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="DY23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="DZ23" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EA23" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EB23" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="EC23" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED23" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EH23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EL23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -11942,10 +11942,10 @@
         <v>25</v>
       </c>
       <c r="DD24" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -11975,7 +11975,7 @@
         <v>3.3</v>
       </c>
       <c r="DO24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12447,7 +12447,7 @@
         <v>2.57</v>
       </c>
       <c r="DO25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP25" t="b">
         <v>0</v>
@@ -12903,7 +12903,7 @@
         <v>1.5</v>
       </c>
       <c r="DO26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13359,7 +13359,7 @@
         <v>3.43</v>
       </c>
       <c r="DO27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13777,7 +13777,7 @@
         <v>1.67</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF28" t="n">
         <v>1</v>
@@ -13807,7 +13807,7 @@
         <v>2.46</v>
       </c>
       <c r="DO28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14230,10 +14230,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF29" t="n">
         <v>0.5</v>
@@ -14263,7 +14263,7 @@
         <v>2.4</v>
       </c>
       <c r="DO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP29" t="b">
         <v>0</v>
@@ -14702,10 +14702,10 @@
         <v>59</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="DF30" t="n">
         <v>0.67</v>
@@ -14735,7 +14735,7 @@
         <v>2.64</v>
       </c>
       <c r="DO30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15169,7 +15169,7 @@
         <v>2</v>
       </c>
       <c r="DE31" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DF31" t="n">
         <v>1.5</v>
@@ -15199,7 +15199,7 @@
         <v>3.4</v>
       </c>
       <c r="DO31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15625,7 +15625,7 @@
         <v>1</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DF32" t="n">
         <v>0.33</v>
@@ -15655,7 +15655,7 @@
         <v>2.5</v>
       </c>
       <c r="DO32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15751,251 +15751,251 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>46116.3125</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
         <v>6</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
+        <v>14</v>
+      </c>
+      <c r="V33" t="n">
+        <v>9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>15</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>3835</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>7625</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
         <v>13</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>19</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>23</v>
-      </c>
-      <c r="X33" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Chuncheon Songam Stadium</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>157 Songam-dong, Chuncheon</t>
-        </is>
-      </c>
-      <c r="AC33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>3831</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>67</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>4448</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>5</v>
-      </c>
       <c r="BO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU33" t="n">
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="BW33" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="BX33" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BY33" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="BZ33" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.22</v>
+        <v>1.18</v>
       </c>
       <c r="CB33" t="n">
-        <v>2.56</v>
+        <v>2.89</v>
       </c>
       <c r="CC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD33" t="n">
         <v>0</v>
       </c>
       <c r="CE33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF33" t="n">
         <v>0</v>
@@ -16013,7 +16013,7 @@
         <v>1</v>
       </c>
       <c r="CK33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL33" t="n">
         <v>0</v>
@@ -16037,82 +16037,82 @@
         <v>22</v>
       </c>
       <c r="CS33" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="CT33" t="n">
         <v>1</v>
       </c>
       <c r="CU33" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV33" t="n">
         <v>16</v>
       </c>
-      <c r="CV33" t="n">
-        <v>23</v>
-      </c>
       <c r="CW33" t="n">
         <v>1</v>
       </c>
       <c r="CX33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CY33" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CZ33" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DA33" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="DB33" t="n">
         <v>25</v>
       </c>
       <c r="DC33" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DG33" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DH33" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="DI33" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="DK33" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.26</v>
+        <v>2.67</v>
       </c>
       <c r="DO33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
         <v>0</v>
@@ -16130,64 +16130,72 @@
       <c r="DX33" t="inlineStr"/>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr"/>
-      <c r="EJ33" t="inlineStr"/>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
       <c r="EK33" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EL33" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.73</t>
         </is>
       </c>
     </row>
@@ -16207,251 +16215,251 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>46116.3125</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>8</v>
       </c>
       <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>19</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>23</v>
+      </c>
+      <c r="X34" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Chuncheon Songam Stadium</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>157 Songam-dong, Chuncheon</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>3831</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>4448</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI34" t="n">
         <v>5</v>
       </c>
-      <c r="L34" t="n">
-        <v>13</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM34" t="n">
         <v>5</v>
       </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>14</v>
-      </c>
-      <c r="V34" t="n">
-        <v>9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>15</v>
-      </c>
-      <c r="X34" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>68</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
-      <c r="AC34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>3835</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
+      <c r="BN34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>102</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY34" t="n">
         <v>63</v>
       </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>7625</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>8</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>13</v>
-      </c>
-      <c r="BO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>55</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>101</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>89</v>
-      </c>
       <c r="BZ34" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.18</v>
+        <v>0.22</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.89</v>
+        <v>2.56</v>
       </c>
       <c r="CC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD34" t="n">
         <v>0</v>
       </c>
       <c r="CE34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF34" t="n">
         <v>0</v>
@@ -16469,7 +16477,7 @@
         <v>1</v>
       </c>
       <c r="CK34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL34" t="n">
         <v>0</v>
@@ -16493,82 +16501,82 @@
         <v>22</v>
       </c>
       <c r="CS34" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
         <v>16</v>
       </c>
-      <c r="CT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="n">
-        <v>13</v>
-      </c>
       <c r="CV34" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY34" t="n">
         <v>16</v>
       </c>
-      <c r="CW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX34" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY34" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ34" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="DA34" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="DB34" t="n">
         <v>25</v>
       </c>
       <c r="DC34" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF34" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DG34" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="DI34" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="DK34" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.67</v>
+        <v>3.26</v>
       </c>
       <c r="DO34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
         <v>0</v>
@@ -16586,72 +16594,64 @@
       <c r="DX34" t="inlineStr"/>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr"/>
+      <c r="EJ34" t="inlineStr"/>
       <c r="EK34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EL34" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.58</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
         <v>2.65</v>
       </c>
       <c r="DO35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17438,7 +17438,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DE36" t="n">
         <v>0.67</v>
@@ -17471,7 +17471,7 @@
         <v>2.36</v>
       </c>
       <c r="DO36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17550,6 +17550,2718 @@
       <c r="EJ36" t="inlineStr"/>
       <c r="EK36" t="inlineStr"/>
       <c r="EL36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46123.20833333334</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>6</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>12</v>
+      </c>
+      <c r="X37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Seoul World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>3833</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>34068</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DJ37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK37" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DN37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="DO37" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP37" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW37" t="inlineStr"/>
+      <c r="DX37" t="inlineStr"/>
+      <c r="DY37" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="DZ37" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EA37" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EB37" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="EC37" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EE37" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EG37" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Jeju United</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>46123.20833333334</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>11</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Steelyard Stadium</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>, Pohang</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>3832</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CB38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU38" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV38" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ38" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA38" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC38" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI38" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ38" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK38" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DN38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DO38" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW38" t="inlineStr"/>
+      <c r="DX38" t="inlineStr"/>
+      <c r="DY38" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="DZ38" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="EA38" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EB38" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="EC38" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF38" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG38" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH38" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EI38" t="inlineStr"/>
+      <c r="EJ38" t="inlineStr"/>
+      <c r="EK38" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EL38" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Gwangju</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>46123.3125</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>9</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6</v>
+      </c>
+      <c r="W39" t="n">
+        <v>10</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Gwangju World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>, Gwangju</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>3852</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>64</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>112</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>4</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA39" t="n">
+        <v>42</v>
+      </c>
+      <c r="DB39" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC39" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF39" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ39" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK39" t="n">
+        <v>59</v>
+      </c>
+      <c r="DL39" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DM39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="DO39" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP39" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV39" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW39" t="inlineStr"/>
+      <c r="DX39" t="inlineStr"/>
+      <c r="DY39" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="DZ39" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="EA39" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EB39" t="inlineStr">
+        <is>
+          <t>6.11</t>
+        </is>
+      </c>
+      <c r="EC39" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EE39" t="inlineStr"/>
+      <c r="EF39" t="inlineStr"/>
+      <c r="EG39" t="inlineStr"/>
+      <c r="EH39" t="inlineStr"/>
+      <c r="EI39" t="inlineStr"/>
+      <c r="EJ39" t="inlineStr"/>
+      <c r="EK39" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EL39" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Ulsan</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>46123.3125</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>6</v>
+      </c>
+      <c r="V40" t="n">
+        <v>4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Sungui Arena Park</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Dowon-dong, Jung-gu, Incheon</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>3836</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA40" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB40" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC40" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DF40" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG40" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DI40" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ40" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO40" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP40" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ40" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR40" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU40" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV40" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW40" t="inlineStr"/>
+      <c r="DX40" t="inlineStr"/>
+      <c r="DY40" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="DZ40" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EA40" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="EB40" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EC40" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EE40" t="inlineStr"/>
+      <c r="EF40" t="inlineStr"/>
+      <c r="EG40" t="inlineStr"/>
+      <c r="EH40" t="inlineStr"/>
+      <c r="EI40" t="inlineStr"/>
+      <c r="EJ40" t="inlineStr"/>
+      <c r="EK40" t="inlineStr"/>
+      <c r="EL40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Gangwon</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46124.20833333334</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>8</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>13</v>
+      </c>
+      <c r="W41" t="n">
+        <v>9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Daejeon World Cup Stadium</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
+        </is>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>3831</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>91</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>130</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CB41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU41" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV41" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ41" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA41" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB41" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC41" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE41" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF41" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG41" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH41" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ41" t="n">
+        <v>84</v>
+      </c>
+      <c r="DK41" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DM41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN41" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DO41" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP41" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ41" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV41" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW41" t="inlineStr"/>
+      <c r="DX41" t="inlineStr"/>
+      <c r="DY41" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="DZ41" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EA41" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EB41" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EC41" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="ED41" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EE41" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF41" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG41" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EH41" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI41" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ41" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EK41" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EL41" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>South_Korea_K_League_1_2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sangju Sangmu</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46124.3125</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>12</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>17</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>14</v>
+      </c>
+      <c r="V42" t="n">
+        <v>10</v>
+      </c>
+      <c r="W42" t="n">
+        <v>9</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>83</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB42" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM42" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CR42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU42" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV42" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ42" t="n">
+        <v>17</v>
+      </c>
+      <c r="DA42" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB42" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC42" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD42" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG42" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH42" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DI42" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ42" t="n">
+        <v>84</v>
+      </c>
+      <c r="DK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DN42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DO42" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP42" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ42" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU42" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV42" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW42" t="inlineStr"/>
+      <c r="DX42" t="inlineStr"/>
+      <c r="DY42" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="DZ42" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EA42" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EB42" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="EC42" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="ED42" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EE42" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF42" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EG42" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EH42" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EI42" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ42" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EK42" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EL42" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
+++ b/data/matches/leagues/South_Korea_K_League_1_2026.xlsx
@@ -597,8 +597,8 @@
     <col width="16.8" customWidth="1" min="24" max="24"/>
     <col width="22.8" customWidth="1" min="25" max="25"/>
     <col width="22.8" customWidth="1" min="26" max="26"/>
-    <col width="36" customWidth="1" min="27" max="27"/>
-    <col width="50" customWidth="1" min="28" max="28"/>
+    <col width="16.8" customWidth="1" min="27" max="27"/>
+    <col width="21.6" customWidth="1" min="28" max="28"/>
     <col width="21.6" customWidth="1" min="29" max="29"/>
     <col width="21.6" customWidth="1" min="30" max="30"/>
     <col width="18" customWidth="1" min="31" max="31"/>
@@ -1514,16 +1514,8 @@
       <c r="Z2" t="n">
         <v>45</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
@@ -1970,16 +1962,8 @@
       <c r="Z3" t="n">
         <v>66</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>2</v>
       </c>
@@ -2906,16 +2890,8 @@
       <c r="Z5" t="n">
         <v>33</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>1</v>
       </c>
@@ -3842,16 +3818,8 @@
       <c r="Z7" t="n">
         <v>40</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
@@ -4298,16 +4266,8 @@
       <c r="Z8" t="n">
         <v>63</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
@@ -4762,16 +4722,8 @@
       <c r="Z9" t="n">
         <v>69</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
@@ -5682,16 +5634,8 @@
       <c r="Z11" t="n">
         <v>51</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>4</v>
       </c>
@@ -6154,16 +6098,8 @@
       <c r="Z12" t="n">
         <v>58</v>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
         <v>3</v>
       </c>
@@ -6618,16 +6554,8 @@
       <c r="Z13" t="n">
         <v>44</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>1</v>
       </c>
@@ -7506,16 +7434,8 @@
       <c r="Z15" t="n">
         <v>54</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>2</v>
       </c>
@@ -8426,16 +8346,8 @@
       <c r="Z17" t="n">
         <v>47</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
         <v>2</v>
       </c>
@@ -9354,16 +9266,8 @@
       <c r="Z19" t="n">
         <v>34</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
         <v>2</v>
       </c>
@@ -10274,16 +10178,8 @@
       <c r="Z21" t="n">
         <v>58</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
         <v>1</v>
       </c>
@@ -10746,16 +10642,8 @@
       <c r="Z22" t="n">
         <v>51</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>3</v>
       </c>
@@ -11210,16 +11098,8 @@
       <c r="Z23" t="n">
         <v>65</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
@@ -11682,16 +11562,8 @@
       <c r="Z24" t="n">
         <v>37</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>2</v>
       </c>
@@ -12154,16 +12026,8 @@
       <c r="Z25" t="n">
         <v>48</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Seoul World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>1</v>
       </c>
@@ -12610,16 +12474,8 @@
       <c r="Z26" t="n">
         <v>63</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
@@ -13514,16 +13370,8 @@
       <c r="Z28" t="n">
         <v>50</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>4</v>
       </c>
@@ -13986,16 +13834,8 @@
       <c r="Z29" t="n">
         <v>70</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>5</v>
       </c>
@@ -14442,16 +14282,8 @@
       <c r="Z30" t="n">
         <v>44</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>1</v>
       </c>
@@ -14906,16 +14738,8 @@
       <c r="Z31" t="n">
         <v>47</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
         <v>2</v>
       </c>
@@ -15810,16 +15634,8 @@
       <c r="Z33" t="n">
         <v>56</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Chuncheon Songam Stadium</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>157 Songam-dong, Chuncheon</t>
-        </is>
-      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>3</v>
       </c>
@@ -16266,16 +16082,8 @@
       <c r="Z34" t="n">
         <v>32</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>1</v>
       </c>
@@ -16730,16 +16538,8 @@
       <c r="Z35" t="n">
         <v>57</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>3</v>
       </c>
@@ -17178,16 +16978,8 @@
       <c r="Z36" t="n">
         <v>57</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>1</v>
       </c>
@@ -17626,16 +17418,8 @@
       <c r="Z37" t="n">
         <v>46</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Seoul World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
-        </is>
-      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
@@ -18090,16 +17874,8 @@
       <c r="Z38" t="n">
         <v>26</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>2</v>
       </c>
@@ -18546,16 +18322,8 @@
       <c r="Z39" t="n">
         <v>50</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>2</v>
       </c>
@@ -18986,16 +18754,8 @@
       <c r="Z40" t="n">
         <v>45</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
         <v>1</v>
       </c>
@@ -19418,16 +19178,8 @@
       <c r="Z41" t="n">
         <v>46</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>0</v>
       </c>
@@ -20338,16 +20090,8 @@
       <c r="Z43" t="n">
         <v>51</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>1</v>
       </c>
@@ -21226,16 +20970,8 @@
       <c r="Z45" t="n">
         <v>41</v>
       </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Seoul World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
-        </is>
-      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
@@ -22146,16 +21882,8 @@
       <c r="Z47" t="n">
         <v>55</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>2</v>
       </c>
@@ -22602,16 +22330,8 @@
       <c r="Z48" t="n">
         <v>51</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
         <v>2</v>
       </c>
@@ -23066,16 +22786,8 @@
       <c r="Z49" t="n">
         <v>39</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>3</v>
       </c>
@@ -23522,16 +23234,8 @@
       <c r="Z50" t="n">
         <v>49</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
@@ -23962,16 +23666,8 @@
       <c r="Z51" t="n">
         <v>33</v>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Seoul World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
-        </is>
-      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
         <v>2</v>
       </c>
@@ -24866,16 +24562,8 @@
       <c r="Z53" t="n">
         <v>40</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Steelyard Stadium</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>, Pohang</t>
-        </is>
-      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
         <v>2</v>
       </c>
@@ -25306,16 +24994,8 @@
       <c r="Z54" t="n">
         <v>47</v>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
         <v>0</v>
       </c>
@@ -25754,16 +25434,8 @@
       <c r="Z55" t="n">
         <v>53</v>
       </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
         <v>1</v>
       </c>
@@ -26642,16 +26314,8 @@
       <c r="Z57" t="n">
         <v>44</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>3</v>
       </c>
@@ -27106,16 +26770,8 @@
       <c r="Z58" t="n">
         <v>58</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>2</v>
       </c>
@@ -27570,16 +27226,8 @@
       <c r="Z59" t="n">
         <v>43</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
         <v>4</v>
       </c>
@@ -28010,16 +27658,8 @@
       <c r="Z60" t="n">
         <v>42</v>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
         <v>3</v>
       </c>
@@ -28458,16 +28098,8 @@
       <c r="Z61" t="n">
         <v>55</v>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>5</v>
       </c>
@@ -28914,16 +28546,8 @@
       <c r="Z62" t="n">
         <v>38</v>
       </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>Seoul World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
-        </is>
-      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
@@ -29362,16 +28986,8 @@
       <c r="Z63" t="n">
         <v>47</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>0</v>
       </c>
@@ -30250,16 +29866,8 @@
       <c r="Z65" t="n">
         <v>48</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
         <v>2</v>
       </c>
@@ -30682,16 +30290,8 @@
       <c r="Z66" t="n">
         <v>57</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
         <v>4</v>
       </c>
@@ -31130,16 +30730,8 @@
       <c r="Z67" t="n">
         <v>38</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>3</v>
       </c>
@@ -31578,16 +31170,8 @@
       <c r="Z68" t="n">
         <v>34</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
         <v>1</v>
       </c>
@@ -32026,16 +31610,8 @@
       <c r="Z69" t="n">
         <v>57</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
         <v>2</v>
       </c>
@@ -33378,16 +32954,8 @@
       <c r="Z72" t="n">
         <v>39</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
         <v>0</v>
       </c>
@@ -33842,16 +33410,8 @@
       <c r="Z73" t="n">
         <v>53</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>Seoul World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>515 Seongsan-dong, Mapo-gu, Sangam, Seoul</t>
-        </is>
-      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
         <v>4</v>
       </c>
@@ -34714,16 +34274,8 @@
       <c r="Z75" t="n">
         <v>64</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
         <v>3</v>
       </c>
@@ -35618,16 +35170,8 @@
       <c r="Z77" t="n">
         <v>30</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
         <v>3</v>
       </c>
@@ -36066,16 +35610,8 @@
       <c r="Z78" t="n">
         <v>55</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
@@ -36530,16 +36066,8 @@
       <c r="Z79" t="n">
         <v>60</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>1</v>
       </c>
@@ -36994,16 +36522,8 @@
       <c r="Z80" t="n">
         <v>63</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>Gwangju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>, Gwangju</t>
-        </is>
-      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>3</v>
       </c>
@@ -37442,16 +36962,8 @@
       <c r="Z81" t="n">
         <v>42</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
         <v>3</v>
       </c>
@@ -38346,16 +37858,8 @@
       <c r="Z83" t="n">
         <v>65</v>
       </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>Ulsan Munsu Football Stadium</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>3302-5 Kozukue, Kohoku-ku, Ulsan</t>
-        </is>
-      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
         <v>0</v>
       </c>
@@ -38810,16 +38314,8 @@
       <c r="Z84" t="n">
         <v>61</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Anyang Stadium</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>1023, Bisan3-dong, Dongan-gu, Anyang</t>
-        </is>
-      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
         <v>2</v>
       </c>
@@ -39242,16 +38738,8 @@
       <c r="Z85" t="n">
         <v>86</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
         <v>5</v>
       </c>
@@ -39690,16 +39178,8 @@
       <c r="Z86" t="n">
         <v>52</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>Daejeon World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>270 Noeun-dong, Yuseong-gu, Daejeon</t>
-        </is>
-      </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
         <v>3</v>
       </c>
@@ -40154,16 +39634,8 @@
       <c r="Z87" t="n">
         <v>45</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>Sungui Arena Park</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>Dowon-dong, Jung-gu, Incheon</t>
-        </is>
-      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
         <v>0</v>
       </c>
@@ -41042,16 +40514,8 @@
       <c r="Z89" t="n">
         <v>42</v>
       </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>Jeonju World Cup Stadium</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>763-1 Banwol-dong, Deokjin-gu, Jeonju</t>
-        </is>
-      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
         <v>1</v>
       </c>
@@ -41490,16 +40954,8 @@
       <c r="Z90" t="n">
         <v>68</v>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Bucheon Stadium</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>San 8, Chunui-dong, Wonmi-gu, Bucheon</t>
-        </is>
-      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
         <v>2</v>
       </c>
@@ -41946,16 +41402,8 @@
       <c r="Z91" t="n">
         <v>50</v>
       </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Chuncheon Songam Stadium</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>157 Songam-dong, Chuncheon</t>
-        </is>
-      </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
         <v>3</v>
       </c>
